--- a/ml/data/raw_transactions_user2.xlsx
+++ b/ml/data/raw_transactions_user2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\朱冠勳\Desktop\專題相關\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\朱冠勳\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E994B53-6B2D-49FD-A088-78A3E9ACBBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F15137-D38B-443F-A36B-86CF9305D07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E1785C59-0982-4302-B1E2-CCE20CEF1A00}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="6">
   <si>
     <t>time_stamp</t>
   </si>
@@ -51,6 +51,10 @@
   </si>
   <si>
     <t>Expense</t>
+  </si>
+  <si>
+    <t>Income</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -437,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B244DA-69FB-4D37-94C6-A16F207C1B02}">
-  <dimension ref="A1:D553"/>
+  <dimension ref="A1:D566"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.06640625" customWidth="1"/>
@@ -613,17 +617,17 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>-1579</v>
+        <v>8521</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -638,67 +642,67 @@
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>-1679</v>
+        <v>8421</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>-1807</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
-        <v>45655</v>
+        <v>45656</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15">
-        <v>435</v>
+        <v>128</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>-2242</v>
+        <v>8193</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
-        <v>45653</v>
+        <v>45655</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16">
-        <v>130</v>
+        <v>435</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>-2372</v>
+        <v>7758</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>-2480</v>
+        <v>7628</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -709,26 +713,26 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>-2507</v>
+        <v>7520</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>-2602</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
@@ -739,26 +743,26 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>-2732</v>
+        <v>7398</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
-        <v>-2837</v>
+        <v>7268</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -769,11 +773,11 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>-3007</v>
+        <v>7163</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
@@ -784,11 +788,11 @@
         <v>4</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>-3057</v>
+        <v>6993</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -799,26 +803,26 @@
         <v>4</v>
       </c>
       <c r="C24">
-        <v>399</v>
+        <v>50</v>
       </c>
       <c r="D24">
         <f t="shared" si="0"/>
-        <v>-3456</v>
+        <v>6943</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>145</v>
+        <v>399</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>-3601</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
@@ -829,26 +833,26 @@
         <v>4</v>
       </c>
       <c r="C26">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>-3715</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
       <c r="C27">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>-3798</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
@@ -859,26 +863,26 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>-3958</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
-        <v>45647</v>
+        <v>45648</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
       <c r="C29">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>-4158</v>
+        <v>6042</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -889,11 +893,11 @@
         <v>4</v>
       </c>
       <c r="C30">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>-4480</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
@@ -904,26 +908,26 @@
         <v>4</v>
       </c>
       <c r="C31">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>-4569</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>-4654</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
@@ -934,26 +938,26 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>-4811</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="D34">
         <f t="shared" si="0"/>
-        <v>-4926</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
@@ -964,26 +968,26 @@
         <v>4</v>
       </c>
       <c r="C35">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>-5024</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>-5139</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
@@ -994,11 +998,11 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>-5189</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -1009,26 +1013,26 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>-5378</v>
+        <v>4811</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
       <c r="C39">
-        <v>580</v>
+        <v>189</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>-5958</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
@@ -1039,11 +1043,11 @@
         <v>4</v>
       </c>
       <c r="C40">
-        <v>151</v>
+        <v>580</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
-        <v>-6109</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
@@ -1054,11 +1058,11 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>-6248</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
@@ -1069,56 +1073,56 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
-        <v>-6468</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D43">
         <f t="shared" si="0"/>
-        <v>-6668</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
-        <v>45641</v>
+        <v>45642</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
       <c r="C44">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="D44">
         <f t="shared" si="0"/>
-        <v>-6772</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>680</v>
+        <v>104</v>
       </c>
       <c r="D45">
         <f t="shared" si="0"/>
-        <v>-7452</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
@@ -1129,26 +1133,26 @@
         <v>4</v>
       </c>
       <c r="C46">
-        <v>378</v>
+        <v>680</v>
       </c>
       <c r="D46">
         <f t="shared" si="0"/>
-        <v>-7830</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47">
-        <v>125</v>
+        <v>378</v>
       </c>
       <c r="D47">
         <f t="shared" si="0"/>
-        <v>-7955</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -1159,41 +1163,41 @@
         <v>4</v>
       </c>
       <c r="C48">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="D48">
         <f t="shared" si="0"/>
-        <v>-8025</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="D49">
         <f t="shared" si="0"/>
-        <v>-8170</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="D50">
         <f t="shared" si="0"/>
-        <v>-8218</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
@@ -1204,11 +1208,11 @@
         <v>4</v>
       </c>
       <c r="C51">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="D51">
         <f t="shared" si="0"/>
-        <v>-8428</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -1219,26 +1223,26 @@
         <v>4</v>
       </c>
       <c r="C52">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="D52">
         <f t="shared" si="0"/>
-        <v>-8513</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="D53">
         <f t="shared" si="0"/>
-        <v>-8703</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
@@ -1249,11 +1253,11 @@
         <v>4</v>
       </c>
       <c r="C54">
-        <v>1200</v>
+        <v>190</v>
       </c>
       <c r="D54">
         <f t="shared" si="0"/>
-        <v>-9903</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -1264,11 +1268,11 @@
         <v>4</v>
       </c>
       <c r="C55">
-        <v>110</v>
+        <v>1200</v>
       </c>
       <c r="D55">
         <f t="shared" si="0"/>
-        <v>-10013</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
@@ -1279,56 +1283,56 @@
         <v>4</v>
       </c>
       <c r="C56">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="D56">
         <f t="shared" si="0"/>
-        <v>-10090</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
       </c>
       <c r="C57">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D57">
         <f t="shared" si="0"/>
-        <v>-10153</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
       </c>
       <c r="C58">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D58">
         <f t="shared" si="0"/>
-        <v>-10258</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="D59">
         <f t="shared" si="0"/>
-        <v>-10433</v>
+        <v>-258</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
@@ -1339,26 +1343,26 @@
         <v>4</v>
       </c>
       <c r="C60">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="D60">
         <f t="shared" si="0"/>
-        <v>-10572</v>
+        <v>-433</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
       <c r="C61">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D61">
         <f t="shared" si="0"/>
-        <v>-10697</v>
+        <v>-572</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
@@ -1369,26 +1373,26 @@
         <v>4</v>
       </c>
       <c r="C62">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D62">
         <f t="shared" si="0"/>
-        <v>-10757</v>
+        <v>-697</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
       <c r="C63">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D63">
         <f t="shared" si="0"/>
-        <v>-10901</v>
+        <v>-757</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
@@ -1399,11 +1403,11 @@
         <v>4</v>
       </c>
       <c r="C64">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="D64">
         <f t="shared" si="0"/>
-        <v>-10951</v>
+        <v>-901</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
@@ -1414,11 +1418,11 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D65">
         <f t="shared" si="0"/>
-        <v>-11101</v>
+        <v>-951</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
@@ -1429,11 +1433,11 @@
         <v>4</v>
       </c>
       <c r="C66">
-        <v>387</v>
+        <v>150</v>
       </c>
       <c r="D66">
         <f t="shared" si="0"/>
-        <v>-11488</v>
+        <v>-1101</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
@@ -1444,26 +1448,26 @@
         <v>4</v>
       </c>
       <c r="C67">
-        <v>550</v>
+        <v>387</v>
       </c>
       <c r="D67">
         <f t="shared" si="0"/>
-        <v>-12038</v>
+        <v>-1488</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="D68">
         <f t="shared" ref="D68:D131" si="1">IF(B68="Income",D67+C68,D67-C68)</f>
-        <v>-12298</v>
+        <v>-2038</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
@@ -1474,521 +1478,521 @@
         <v>4</v>
       </c>
       <c r="C69">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="D69">
         <f t="shared" si="1"/>
-        <v>-12426</v>
+        <v>-2298</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
-        <v>-12481</v>
+        <v>-2426</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
       <c r="C71">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="D71">
         <f t="shared" si="1"/>
-        <v>-12583</v>
+        <v>-2481</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72">
-        <v>147</v>
+        <v>10000</v>
       </c>
       <c r="D72">
         <f t="shared" si="1"/>
-        <v>-12730</v>
+        <v>7519</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="D73">
         <f t="shared" si="1"/>
-        <v>-12805</v>
+        <v>7417</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
       <c r="C74">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D74">
         <f t="shared" si="1"/>
-        <v>-12925</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
       <c r="C75">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D75">
         <f t="shared" si="1"/>
-        <v>-13023</v>
+        <v>7195</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D76">
         <f t="shared" si="1"/>
-        <v>-13123</v>
+        <v>7075</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D77">
         <f t="shared" si="1"/>
-        <v>-13173</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D78">
         <f t="shared" si="1"/>
-        <v>-13298</v>
+        <v>6877</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
-        <v>430</v>
+        <v>50</v>
       </c>
       <c r="D79">
         <f t="shared" si="1"/>
-        <v>-13728</v>
+        <v>6827</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
-        <v>45619</v>
+        <v>45622</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="D80">
         <f t="shared" si="1"/>
-        <v>-13778</v>
+        <v>6702</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="D81">
         <f t="shared" si="1"/>
-        <v>-13898</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
-        <v>45617</v>
+        <v>45619</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
       <c r="C82">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="D82">
         <f t="shared" si="1"/>
-        <v>-14073</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
-        <v>45616</v>
+        <v>45618</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D83">
         <f t="shared" si="1"/>
-        <v>-14233</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>411</v>
+        <v>175</v>
       </c>
       <c r="D84">
         <f t="shared" si="1"/>
-        <v>-14644</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D85">
         <f t="shared" si="1"/>
-        <v>-14799</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>113</v>
+        <v>411</v>
       </c>
       <c r="D86">
         <f t="shared" si="1"/>
-        <v>-14912</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="D87">
         <f t="shared" si="1"/>
-        <v>-15012</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D88">
         <f t="shared" si="1"/>
-        <v>-15128</v>
+        <v>5088</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
-        <v>45611</v>
+        <v>45614</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D89">
         <f t="shared" si="1"/>
-        <v>-15262</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
-        <v>45611</v>
+        <v>45614</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
       <c r="C90">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D90">
         <f t="shared" si="1"/>
-        <v>-15392</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
-        <v>45609</v>
+        <v>45611</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D91">
         <f t="shared" si="1"/>
-        <v>-15522</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
-        <v>45609</v>
+        <v>45611</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D92">
         <f t="shared" si="1"/>
-        <v>-15607</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
       <c r="C93">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D93">
         <f t="shared" si="1"/>
-        <v>-15707</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="D94">
         <f t="shared" si="1"/>
-        <v>-15845</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="D95">
         <f t="shared" si="1"/>
-        <v>-16745</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96">
-        <v>536</v>
+        <v>138</v>
       </c>
       <c r="D96">
         <f t="shared" si="1"/>
-        <v>-17281</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
-        <v>45606</v>
+        <v>45607</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="D97">
         <f t="shared" si="1"/>
-        <v>-17366</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
       <c r="C98">
-        <v>91</v>
+        <v>536</v>
       </c>
       <c r="D98">
         <f t="shared" si="1"/>
-        <v>-17457</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
-        <v>45604</v>
+        <v>45606</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="D99">
         <f t="shared" si="1"/>
-        <v>-17607</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
       <c r="C100">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="D100">
         <f t="shared" si="1"/>
-        <v>-17657</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
       <c r="C101">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D101">
         <f t="shared" si="1"/>
-        <v>-17792</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
       <c r="C102">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="D102">
         <f t="shared" si="1"/>
-        <v>-17927</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
       <c r="C103">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D103">
         <f t="shared" si="1"/>
-        <v>-18023</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
@@ -1999,221 +2003,221 @@
         <v>4</v>
       </c>
       <c r="C104">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="D104">
         <f t="shared" si="1"/>
-        <v>-18108</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D105">
         <f t="shared" si="1"/>
-        <v>-18218</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="D106">
         <f t="shared" si="1"/>
-        <v>-18428</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
-        <v>45598</v>
+        <v>45601</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D107">
         <f t="shared" si="1"/>
-        <v>-18498</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
-        <v>45598</v>
+        <v>45601</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="D108">
         <f t="shared" si="1"/>
-        <v>-18588</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="D109">
         <f t="shared" si="1"/>
-        <v>-18719</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="D110">
         <f t="shared" si="1"/>
-        <v>-18854</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
       <c r="C111">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="D111">
         <f t="shared" si="1"/>
-        <v>-19061</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
       <c r="C112">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="D112">
         <f t="shared" si="1"/>
-        <v>-19260</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
-        <v>45595</v>
+        <v>45597</v>
       </c>
       <c r="B113" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113">
-        <v>110</v>
+        <v>10000</v>
       </c>
       <c r="D113">
         <f t="shared" si="1"/>
-        <v>-19370</v>
+        <v>11146</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
       <c r="C114">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="D114">
         <f t="shared" si="1"/>
-        <v>-19643</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
       <c r="C115">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="D115">
         <f t="shared" si="1"/>
-        <v>-19698</v>
+        <v>10740</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D116">
         <f t="shared" si="1"/>
-        <v>-19767</v>
+        <v>10630</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="1">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
       <c r="C117">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="D117">
         <f t="shared" si="1"/>
-        <v>-19867</v>
+        <v>10357</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="1">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
       <c r="C118">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D118">
         <f t="shared" si="1"/>
-        <v>-19927</v>
+        <v>10302</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.45">
@@ -2224,206 +2228,206 @@
         <v>4</v>
       </c>
       <c r="C119">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="D119">
         <f t="shared" si="1"/>
-        <v>-20062</v>
+        <v>10233</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="1">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
       <c r="C120">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="D120">
         <f t="shared" si="1"/>
-        <v>-20226</v>
+        <v>10133</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="1">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
       <c r="C121">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="D121">
         <f t="shared" si="1"/>
-        <v>-20386</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D122">
         <f t="shared" si="1"/>
-        <v>-20546</v>
+        <v>9938</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="1">
-        <v>45591</v>
+        <v>45593</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
       <c r="C123">
-        <v>1100</v>
+        <v>164</v>
       </c>
       <c r="D123">
         <f t="shared" si="1"/>
-        <v>-21646</v>
+        <v>9774</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="1">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
       <c r="C124">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D124">
         <f t="shared" si="1"/>
-        <v>-21746</v>
+        <v>9614</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
       <c r="C125">
-        <v>679</v>
+        <v>160</v>
       </c>
       <c r="D125">
         <f t="shared" si="1"/>
-        <v>-22425</v>
+        <v>9454</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="1">
-        <v>45589</v>
+        <v>45591</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
       <c r="C126">
-        <v>96</v>
+        <v>1100</v>
       </c>
       <c r="D126">
         <f t="shared" si="1"/>
-        <v>-22521</v>
+        <v>8354</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="1">
-        <v>45588</v>
+        <v>45590</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
       <c r="C127">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D127">
         <f t="shared" si="1"/>
-        <v>-22576</v>
+        <v>8254</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
-        <v>45588</v>
+        <v>45590</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
       <c r="C128">
-        <v>110</v>
+        <v>679</v>
       </c>
       <c r="D128">
         <f t="shared" si="1"/>
-        <v>-22686</v>
+        <v>7575</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="1">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
       <c r="C129">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D129">
         <f t="shared" si="1"/>
-        <v>-22755</v>
+        <v>7479</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" s="1">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
       </c>
       <c r="C130">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D130">
         <f t="shared" si="1"/>
-        <v>-22815</v>
+        <v>7424</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="D131">
         <f t="shared" si="1"/>
-        <v>-22825</v>
+        <v>7314</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="1">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
       </c>
       <c r="C132">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="D132">
         <f t="shared" ref="D132:D195" si="2">IF(B132="Income",D131+C132,D131-C132)</f>
-        <v>-22995</v>
+        <v>7245</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
@@ -2434,256 +2438,256 @@
         <v>4</v>
       </c>
       <c r="C133">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D133">
         <f t="shared" si="2"/>
-        <v>-23070</v>
+        <v>7185</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
       <c r="C134">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="D134">
         <f t="shared" si="2"/>
-        <v>-23147</v>
+        <v>7175</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="1">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
       </c>
       <c r="C135">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="D135">
         <f t="shared" si="2"/>
-        <v>-23237</v>
+        <v>7005</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="1">
-        <v>45583</v>
+        <v>45587</v>
       </c>
       <c r="B136" t="s">
         <v>4</v>
       </c>
       <c r="C136">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D136">
         <f t="shared" si="2"/>
-        <v>-23322</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
-        <v>45580</v>
+        <v>45586</v>
       </c>
       <c r="B137" t="s">
         <v>4</v>
       </c>
       <c r="C137">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D137">
         <f t="shared" si="2"/>
-        <v>-23442</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="1">
-        <v>45579</v>
+        <v>45586</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
       </c>
       <c r="C138">
-        <v>265</v>
+        <v>90</v>
       </c>
       <c r="D138">
         <f t="shared" si="2"/>
-        <v>-23707</v>
+        <v>6763</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="1">
-        <v>45576</v>
+        <v>45583</v>
       </c>
       <c r="B139" t="s">
         <v>4</v>
       </c>
       <c r="C139">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D139">
         <f t="shared" si="2"/>
-        <v>-23787</v>
+        <v>6678</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
-        <v>45576</v>
+        <v>45580</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
       <c r="C140">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="D140">
         <f t="shared" si="2"/>
-        <v>-23957</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="1">
-        <v>45575</v>
+        <v>45579</v>
       </c>
       <c r="B141" t="s">
         <v>4</v>
       </c>
       <c r="C141">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="D141">
         <f t="shared" si="2"/>
-        <v>-24082</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="1">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
       </c>
       <c r="C142">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="D142">
         <f t="shared" si="2"/>
-        <v>-24292</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
-        <v>45574</v>
+        <v>45576</v>
       </c>
       <c r="B143" t="s">
         <v>4</v>
       </c>
       <c r="C143">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="D143">
         <f t="shared" si="2"/>
-        <v>-24362</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="1">
-        <v>45573</v>
+        <v>45575</v>
       </c>
       <c r="B144" t="s">
         <v>4</v>
       </c>
       <c r="C144">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D144">
         <f t="shared" si="2"/>
-        <v>-24497</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
-        <v>45573</v>
+        <v>45575</v>
       </c>
       <c r="B145" t="s">
         <v>4</v>
       </c>
       <c r="C145">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D145">
         <f t="shared" si="2"/>
-        <v>-24686</v>
+        <v>5708</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="1">
-        <v>45572</v>
+        <v>45574</v>
       </c>
       <c r="B146" t="s">
         <v>4</v>
       </c>
       <c r="C146">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="D146">
         <f t="shared" si="2"/>
-        <v>-24811</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="1">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="B147" t="s">
         <v>4</v>
       </c>
       <c r="C147">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="D147">
         <f t="shared" si="2"/>
-        <v>-24881</v>
+        <v>5503</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="1">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="B148" t="s">
         <v>4</v>
       </c>
       <c r="C148">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="D148">
         <f t="shared" si="2"/>
-        <v>-24966</v>
+        <v>5314</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="1">
-        <v>45571</v>
+        <v>45572</v>
       </c>
       <c r="B149" t="s">
         <v>4</v>
       </c>
       <c r="C149">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D149">
         <f t="shared" si="2"/>
-        <v>-25071</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="1">
-        <v>45571</v>
+        <v>45572</v>
       </c>
       <c r="B150" t="s">
         <v>4</v>
@@ -2693,112 +2697,112 @@
       </c>
       <c r="D150">
         <f t="shared" si="2"/>
-        <v>-25141</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="1">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="B151" t="s">
         <v>4</v>
       </c>
       <c r="C151">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D151">
         <f t="shared" si="2"/>
-        <v>-25231</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="1">
-        <v>45569</v>
+        <v>45571</v>
       </c>
       <c r="B152" t="s">
         <v>4</v>
       </c>
       <c r="C152">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D152">
         <f t="shared" si="2"/>
-        <v>-25309</v>
+        <v>4929</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" s="1">
-        <v>45568</v>
+        <v>45571</v>
       </c>
       <c r="B153" t="s">
         <v>4</v>
       </c>
       <c r="C153">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="D153">
         <f t="shared" si="2"/>
-        <v>-25445</v>
+        <v>4859</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" s="1">
-        <v>45567</v>
+        <v>45569</v>
       </c>
       <c r="B154" t="s">
         <v>4</v>
       </c>
       <c r="C154">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="D154">
         <f t="shared" si="2"/>
-        <v>-25605</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" s="1">
-        <v>45566</v>
+        <v>45569</v>
       </c>
       <c r="B155" t="s">
         <v>4</v>
       </c>
       <c r="C155">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="D155">
         <f t="shared" si="2"/>
-        <v>-25615</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" s="1">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="B156" t="s">
         <v>4</v>
       </c>
       <c r="C156">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D156">
         <f t="shared" si="2"/>
-        <v>-25730</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" s="1">
-        <v>45566</v>
+        <v>45567</v>
       </c>
       <c r="B157" t="s">
         <v>4</v>
       </c>
       <c r="C157">
-        <v>510</v>
+        <v>160</v>
       </c>
       <c r="D157">
         <f t="shared" si="2"/>
-        <v>-26240</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.45">
@@ -2809,166 +2813,166 @@
         <v>4</v>
       </c>
       <c r="C158">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="D158">
         <f t="shared" si="2"/>
-        <v>-26470</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" s="1">
-        <v>45565</v>
+        <v>45566</v>
       </c>
       <c r="B159" t="s">
         <v>4</v>
       </c>
       <c r="C159">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="D159">
         <f t="shared" si="2"/>
-        <v>-26511</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A160" s="1">
-        <v>45563</v>
+        <v>45566</v>
       </c>
       <c r="B160" t="s">
         <v>4</v>
       </c>
       <c r="C160">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="D160">
         <f t="shared" si="2"/>
-        <v>-26661</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" s="1">
-        <v>45563</v>
+        <v>45566</v>
       </c>
       <c r="B161" t="s">
         <v>4</v>
       </c>
       <c r="C161">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="D161">
         <f t="shared" si="2"/>
-        <v>-26761</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="1">
-        <v>45563</v>
+        <v>45566</v>
       </c>
       <c r="B162" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C162">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="D162">
         <f t="shared" si="2"/>
-        <v>-26861</v>
+        <v>13530</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" s="1">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="B163" t="s">
         <v>4</v>
       </c>
       <c r="C163">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="D163">
         <f t="shared" si="2"/>
-        <v>-26961</v>
+        <v>13489</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A164" s="1">
-        <v>45561</v>
+        <v>45563</v>
       </c>
       <c r="B164" t="s">
         <v>4</v>
       </c>
       <c r="C164">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D164">
         <f t="shared" si="2"/>
-        <v>-27109</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" s="1">
-        <v>45561</v>
+        <v>45563</v>
       </c>
       <c r="B165" t="s">
         <v>4</v>
       </c>
       <c r="C165">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D165">
         <f t="shared" si="2"/>
-        <v>-27229</v>
+        <v>13239</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A166" s="1">
-        <v>45560</v>
+        <v>45563</v>
       </c>
       <c r="B166" t="s">
         <v>4</v>
       </c>
       <c r="C166">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D166">
         <f t="shared" si="2"/>
-        <v>-27274</v>
+        <v>13139</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" s="1">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="B167" t="s">
         <v>4</v>
       </c>
       <c r="C167">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="D167">
         <f t="shared" si="2"/>
-        <v>-27414</v>
+        <v>13039</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="1">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="B168" t="s">
         <v>4</v>
       </c>
       <c r="C168">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="D168">
         <f t="shared" si="2"/>
-        <v>-27484</v>
+        <v>12891</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="1">
-        <v>45559</v>
+        <v>45561</v>
       </c>
       <c r="B169" t="s">
         <v>4</v>
@@ -2978,457 +2982,457 @@
       </c>
       <c r="D169">
         <f t="shared" si="2"/>
-        <v>-27604</v>
+        <v>12771</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" s="1">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="B170" t="s">
         <v>4</v>
       </c>
       <c r="C170">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="D170">
         <f t="shared" si="2"/>
-        <v>-27720</v>
+        <v>12726</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" s="1">
-        <v>45558</v>
+        <v>45560</v>
       </c>
       <c r="B171" t="s">
         <v>4</v>
       </c>
       <c r="C171">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="D171">
         <f t="shared" si="2"/>
-        <v>-27775</v>
+        <v>12586</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" s="1">
-        <v>45558</v>
+        <v>45560</v>
       </c>
       <c r="B172" t="s">
         <v>4</v>
       </c>
       <c r="C172">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D172">
         <f t="shared" si="2"/>
-        <v>-27860</v>
+        <v>12516</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" s="1">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="B173" t="s">
         <v>4</v>
       </c>
       <c r="C173">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D173">
         <f t="shared" si="2"/>
-        <v>-27910</v>
+        <v>12396</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" s="1">
-        <v>45555</v>
+        <v>45559</v>
       </c>
       <c r="B174" t="s">
         <v>4</v>
       </c>
       <c r="C174">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D174">
         <f t="shared" si="2"/>
-        <v>-27995</v>
+        <v>12280</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" s="1">
-        <v>45554</v>
+        <v>45558</v>
       </c>
       <c r="B175" t="s">
         <v>4</v>
       </c>
       <c r="C175">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D175">
         <f t="shared" si="2"/>
-        <v>-28114</v>
+        <v>12225</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" s="1">
-        <v>45554</v>
+        <v>45558</v>
       </c>
       <c r="B176" t="s">
         <v>4</v>
       </c>
       <c r="C176">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D176">
         <f t="shared" si="2"/>
-        <v>-28194</v>
+        <v>12140</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" s="1">
-        <v>45553</v>
+        <v>45558</v>
       </c>
       <c r="B177" t="s">
         <v>4</v>
       </c>
       <c r="C177">
-        <v>3200</v>
+        <v>50</v>
       </c>
       <c r="D177">
         <f t="shared" si="2"/>
-        <v>-31394</v>
+        <v>12090</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" s="1">
-        <v>45553</v>
+        <v>45555</v>
       </c>
       <c r="B178" t="s">
         <v>4</v>
       </c>
       <c r="C178">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D178">
         <f t="shared" si="2"/>
-        <v>-31434</v>
+        <v>12005</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" s="1">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="B179" t="s">
         <v>4</v>
       </c>
       <c r="C179">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D179">
         <f t="shared" si="2"/>
-        <v>-31534</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" s="1">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="B180" t="s">
         <v>4</v>
       </c>
       <c r="C180">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D180">
         <f t="shared" si="2"/>
-        <v>-31623</v>
+        <v>11806</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" s="1">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="B181" t="s">
         <v>4</v>
       </c>
       <c r="C181">
-        <v>68</v>
+        <v>3200</v>
       </c>
       <c r="D181">
         <f t="shared" si="2"/>
-        <v>-31691</v>
+        <v>8606</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" s="1">
-        <v>45551</v>
+        <v>45553</v>
       </c>
       <c r="B182" t="s">
         <v>4</v>
       </c>
       <c r="C182">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="D182">
         <f t="shared" si="2"/>
-        <v>-31825</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" s="1">
-        <v>45548</v>
+        <v>45553</v>
       </c>
       <c r="B183" t="s">
         <v>4</v>
       </c>
       <c r="C183">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D183">
         <f t="shared" si="2"/>
-        <v>-31899</v>
+        <v>8466</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" s="1">
-        <v>45548</v>
+        <v>45553</v>
       </c>
       <c r="B184" t="s">
         <v>4</v>
       </c>
       <c r="C184">
-        <v>600</v>
+        <v>89</v>
       </c>
       <c r="D184">
         <f t="shared" si="2"/>
-        <v>-32499</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" s="1">
-        <v>45547</v>
+        <v>45552</v>
       </c>
       <c r="B185" t="s">
         <v>4</v>
       </c>
       <c r="C185">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D185">
         <f t="shared" si="2"/>
-        <v>-32619</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A186" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="B186" t="s">
         <v>4</v>
       </c>
       <c r="C186">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="D186">
         <f t="shared" si="2"/>
-        <v>-32727</v>
+        <v>8175</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A187" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="B187" t="s">
         <v>4</v>
       </c>
       <c r="C187">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D187">
         <f t="shared" si="2"/>
-        <v>-32812</v>
+        <v>8101</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="B188" t="s">
         <v>4</v>
       </c>
       <c r="C188">
-        <v>83</v>
+        <v>600</v>
       </c>
       <c r="D188">
         <f t="shared" si="2"/>
-        <v>-32895</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A189" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="B189" t="s">
         <v>4</v>
       </c>
       <c r="C189">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="D189">
         <f t="shared" si="2"/>
-        <v>-33102</v>
+        <v>7381</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="B190" t="s">
         <v>4</v>
       </c>
       <c r="C190">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="D190">
         <f t="shared" si="2"/>
-        <v>-33172</v>
+        <v>7273</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A191" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="B191" t="s">
         <v>4</v>
       </c>
       <c r="C191">
-        <v>522</v>
+        <v>85</v>
       </c>
       <c r="D191">
         <f t="shared" si="2"/>
-        <v>-33694</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A192" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="B192" t="s">
         <v>4</v>
       </c>
       <c r="C192">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="D192">
         <f t="shared" si="2"/>
-        <v>-33904</v>
+        <v>7105</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="B193" t="s">
         <v>4</v>
       </c>
       <c r="C193">
-        <v>364</v>
+        <v>207</v>
       </c>
       <c r="D193">
         <f t="shared" si="2"/>
-        <v>-34268</v>
+        <v>6898</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A194" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="B194" t="s">
         <v>4</v>
       </c>
       <c r="C194">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="D194">
         <f t="shared" si="2"/>
-        <v>-34438</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A195" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="B195" t="s">
         <v>4</v>
       </c>
       <c r="C195">
-        <v>200</v>
+        <v>522</v>
       </c>
       <c r="D195">
         <f t="shared" si="2"/>
-        <v>-34638</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A196" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="B196" t="s">
         <v>4</v>
       </c>
       <c r="C196">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="D196">
         <f t="shared" ref="D196:D259" si="3">IF(B196="Income",D195+C196,D195-C196)</f>
-        <v>-34683</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A197" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="B197" t="s">
         <v>4</v>
       </c>
       <c r="C197">
-        <v>50</v>
+        <v>364</v>
       </c>
       <c r="D197">
         <f t="shared" si="3"/>
-        <v>-34733</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A198" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="B198" t="s">
         <v>4</v>
       </c>
       <c r="C198">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="D198">
         <f t="shared" si="3"/>
-        <v>-34823</v>
+        <v>5562</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="B199" t="s">
         <v>4</v>
       </c>
       <c r="C199">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D199">
         <f t="shared" si="3"/>
-        <v>-35063</v>
+        <v>5362</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.45">
@@ -3439,271 +3443,271 @@
         <v>4</v>
       </c>
       <c r="C200">
-        <v>429</v>
+        <v>45</v>
       </c>
       <c r="D200">
         <f t="shared" si="3"/>
-        <v>-35492</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" s="1">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="B201" t="s">
         <v>4</v>
       </c>
       <c r="C201">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D201">
         <f t="shared" si="3"/>
-        <v>-35592</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A202" s="1">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="B202" t="s">
         <v>4</v>
       </c>
       <c r="C202">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D202">
         <f t="shared" si="3"/>
-        <v>-35702</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A203" s="1">
-        <v>45535</v>
+        <v>45544</v>
       </c>
       <c r="B203" t="s">
         <v>4</v>
       </c>
       <c r="C203">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="D203">
         <f t="shared" si="3"/>
-        <v>-35842</v>
+        <v>4937</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A204" s="1">
-        <v>45534</v>
+        <v>45544</v>
       </c>
       <c r="B204" t="s">
         <v>4</v>
       </c>
       <c r="C204">
-        <v>30</v>
+        <v>429</v>
       </c>
       <c r="D204">
         <f t="shared" si="3"/>
-        <v>-35872</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A205" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="B205" t="s">
         <v>4</v>
       </c>
       <c r="C205">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="D205">
         <f t="shared" si="3"/>
-        <v>-36152</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A206" s="1">
-        <v>45533</v>
+        <v>45541</v>
       </c>
       <c r="B206" t="s">
         <v>4</v>
       </c>
       <c r="C206">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D206">
         <f t="shared" si="3"/>
-        <v>-36252</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A207" s="1">
-        <v>45533</v>
+        <v>45536</v>
       </c>
       <c r="B207" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C207">
-        <v>260</v>
+        <v>10000</v>
       </c>
       <c r="D207">
         <f t="shared" si="3"/>
-        <v>-36512</v>
+        <v>14298</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" s="1">
-        <v>45531</v>
+        <v>45535</v>
       </c>
       <c r="B208" t="s">
         <v>4</v>
       </c>
       <c r="C208">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="D208">
         <f t="shared" si="3"/>
-        <v>-36537</v>
+        <v>14158</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" s="1">
-        <v>45530</v>
+        <v>45534</v>
       </c>
       <c r="B209" t="s">
         <v>4</v>
       </c>
       <c r="C209">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="D209">
         <f t="shared" si="3"/>
-        <v>-36706</v>
+        <v>14128</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A210" s="1">
-        <v>45530</v>
+        <v>45534</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
       </c>
       <c r="C210">
-        <v>401</v>
+        <v>280</v>
       </c>
       <c r="D210">
         <f t="shared" si="3"/>
-        <v>-37107</v>
+        <v>13848</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A211" s="1">
-        <v>45530</v>
+        <v>45533</v>
       </c>
       <c r="B211" t="s">
         <v>4</v>
       </c>
       <c r="C211">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="D211">
         <f t="shared" si="3"/>
-        <v>-37173</v>
+        <v>13748</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A212" s="1">
-        <v>45530</v>
+        <v>45533</v>
       </c>
       <c r="B212" t="s">
         <v>4</v>
       </c>
       <c r="C212">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="D212">
         <f t="shared" si="3"/>
-        <v>-37273</v>
+        <v>13488</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A213" s="1">
-        <v>45529</v>
+        <v>45531</v>
       </c>
       <c r="B213" t="s">
         <v>4</v>
       </c>
       <c r="C213">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D213">
         <f t="shared" si="3"/>
-        <v>-37373</v>
+        <v>13463</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A214" s="1">
-        <v>45526</v>
+        <v>45530</v>
       </c>
       <c r="B214" t="s">
         <v>4</v>
       </c>
       <c r="C214">
-        <v>428</v>
+        <v>169</v>
       </c>
       <c r="D214">
         <f t="shared" si="3"/>
-        <v>-37801</v>
+        <v>13294</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A215" s="1">
-        <v>45526</v>
+        <v>45530</v>
       </c>
       <c r="B215" t="s">
         <v>4</v>
       </c>
       <c r="C215">
-        <v>40</v>
+        <v>401</v>
       </c>
       <c r="D215">
         <f t="shared" si="3"/>
-        <v>-37841</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A216" s="1">
-        <v>45526</v>
+        <v>45530</v>
       </c>
       <c r="B216" t="s">
         <v>4</v>
       </c>
       <c r="C216">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="D216">
         <f t="shared" si="3"/>
-        <v>-38001</v>
+        <v>12827</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" s="1">
-        <v>45526</v>
+        <v>45530</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
       </c>
       <c r="C217">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="D217">
         <f t="shared" si="3"/>
-        <v>-38231</v>
+        <v>12727</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A218" s="1">
-        <v>45526</v>
+        <v>45529</v>
       </c>
       <c r="B218" t="s">
         <v>4</v>
@@ -3713,382 +3717,382 @@
       </c>
       <c r="D218">
         <f t="shared" si="3"/>
-        <v>-38331</v>
+        <v>12627</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A219" s="1">
-        <v>45523</v>
+        <v>45526</v>
       </c>
       <c r="B219" t="s">
         <v>4</v>
       </c>
       <c r="C219">
-        <v>96</v>
+        <v>428</v>
       </c>
       <c r="D219">
         <f t="shared" si="3"/>
-        <v>-38427</v>
+        <v>12199</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A220" s="1">
-        <v>45523</v>
+        <v>45526</v>
       </c>
       <c r="B220" t="s">
         <v>4</v>
       </c>
       <c r="C220">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D220">
         <f t="shared" si="3"/>
-        <v>-38497</v>
+        <v>12159</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A221" s="1">
-        <v>45514</v>
+        <v>45526</v>
       </c>
       <c r="B221" t="s">
         <v>4</v>
       </c>
       <c r="C221">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D221">
         <f t="shared" si="3"/>
-        <v>-38597</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A222" s="1">
-        <v>45506</v>
+        <v>45526</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
       </c>
       <c r="C222">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="D222">
         <f t="shared" si="3"/>
-        <v>-38697</v>
+        <v>11769</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A223" s="1">
-        <v>45506</v>
+        <v>45526</v>
       </c>
       <c r="B223" t="s">
         <v>4</v>
       </c>
       <c r="C223">
-        <v>460</v>
+        <v>100</v>
       </c>
       <c r="D223">
         <f t="shared" si="3"/>
-        <v>-39157</v>
+        <v>11669</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A224" s="1">
-        <v>45506</v>
+        <v>45523</v>
       </c>
       <c r="B224" t="s">
         <v>4</v>
       </c>
       <c r="C224">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D224">
         <f t="shared" si="3"/>
-        <v>-39257</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" s="1">
-        <v>45502</v>
+        <v>45523</v>
       </c>
       <c r="B225" t="s">
         <v>4</v>
       </c>
       <c r="C225">
-        <v>3700</v>
+        <v>70</v>
       </c>
       <c r="D225">
         <f t="shared" si="3"/>
-        <v>-42957</v>
+        <v>11503</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" s="1">
-        <v>45501</v>
+        <v>45514</v>
       </c>
       <c r="B226" t="s">
         <v>4</v>
       </c>
       <c r="C226">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D226">
         <f t="shared" si="3"/>
-        <v>-43077</v>
+        <v>11403</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A227" s="1">
-        <v>45499</v>
+        <v>45506</v>
       </c>
       <c r="B227" t="s">
         <v>4</v>
       </c>
       <c r="C227">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="D227">
         <f t="shared" si="3"/>
-        <v>-43212</v>
+        <v>11303</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" s="1">
-        <v>45499</v>
+        <v>45506</v>
       </c>
       <c r="B228" t="s">
         <v>4</v>
       </c>
       <c r="C228">
-        <v>100</v>
+        <v>460</v>
       </c>
       <c r="D228">
         <f t="shared" si="3"/>
-        <v>-43312</v>
+        <v>10843</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A229" s="1">
-        <v>45498</v>
+        <v>45506</v>
       </c>
       <c r="B229" t="s">
         <v>4</v>
       </c>
       <c r="C229">
-        <v>605</v>
+        <v>100</v>
       </c>
       <c r="D229">
         <f t="shared" si="3"/>
-        <v>-43917</v>
+        <v>10743</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A230" s="1">
-        <v>45495</v>
+        <v>45505</v>
       </c>
       <c r="B230" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C230">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="D230">
         <f t="shared" si="3"/>
-        <v>-44217</v>
+        <v>20743</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A231" s="1">
-        <v>45490</v>
+        <v>45502</v>
       </c>
       <c r="B231" t="s">
         <v>4</v>
       </c>
       <c r="C231">
-        <v>100</v>
+        <v>3700</v>
       </c>
       <c r="D231">
         <f t="shared" si="3"/>
-        <v>-44317</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A232" s="1">
-        <v>45490</v>
+        <v>45501</v>
       </c>
       <c r="B232" t="s">
         <v>4</v>
       </c>
       <c r="C232">
-        <v>304</v>
+        <v>120</v>
       </c>
       <c r="D232">
         <f t="shared" si="3"/>
-        <v>-44621</v>
+        <v>16923</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" s="1">
-        <v>45485</v>
+        <v>45499</v>
       </c>
       <c r="B233" t="s">
         <v>4</v>
       </c>
       <c r="C233">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="D233">
         <f t="shared" si="3"/>
-        <v>-44818</v>
+        <v>16788</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A234" s="1">
-        <v>45485</v>
+        <v>45499</v>
       </c>
       <c r="B234" t="s">
         <v>4</v>
       </c>
       <c r="C234">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D234">
         <f t="shared" si="3"/>
-        <v>-44873</v>
+        <v>16688</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" s="1">
-        <v>45485</v>
+        <v>45498</v>
       </c>
       <c r="B235" t="s">
         <v>4</v>
       </c>
       <c r="C235">
-        <v>35</v>
+        <v>605</v>
       </c>
       <c r="D235">
         <f t="shared" si="3"/>
-        <v>-44908</v>
+        <v>16083</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A236" s="1">
-        <v>45485</v>
+        <v>45495</v>
       </c>
       <c r="B236" t="s">
         <v>4</v>
       </c>
       <c r="C236">
-        <v>167</v>
+        <v>300</v>
       </c>
       <c r="D236">
         <f t="shared" si="3"/>
-        <v>-45075</v>
+        <v>15783</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A237" s="1">
-        <v>45485</v>
+        <v>45490</v>
       </c>
       <c r="B237" t="s">
         <v>4</v>
       </c>
       <c r="C237">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D237">
         <f t="shared" si="3"/>
-        <v>-45170</v>
+        <v>15683</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A238" s="1">
-        <v>45484</v>
+        <v>45490</v>
       </c>
       <c r="B238" t="s">
         <v>4</v>
       </c>
       <c r="C238">
-        <v>40</v>
+        <v>304</v>
       </c>
       <c r="D238">
         <f t="shared" si="3"/>
-        <v>-45210</v>
+        <v>15379</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A239" s="1">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B239" t="s">
         <v>4</v>
       </c>
       <c r="C239">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="D239">
         <f t="shared" si="3"/>
-        <v>-45242</v>
+        <v>15182</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A240" s="1">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B240" t="s">
         <v>4</v>
       </c>
       <c r="C240">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D240">
         <f t="shared" si="3"/>
-        <v>-45275</v>
+        <v>15127</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" s="1">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B241" t="s">
         <v>4</v>
       </c>
       <c r="C241">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D241">
         <f t="shared" si="3"/>
-        <v>-45372</v>
+        <v>15092</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A242" s="1">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B242" t="s">
         <v>4</v>
       </c>
       <c r="C242">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="D242">
         <f t="shared" si="3"/>
-        <v>-45412</v>
+        <v>14925</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" s="1">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B243" t="s">
         <v>4</v>
       </c>
       <c r="C243">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="D243">
         <f t="shared" si="3"/>
-        <v>-45462</v>
+        <v>14830</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
@@ -4099,11 +4103,11 @@
         <v>4</v>
       </c>
       <c r="C244">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D244">
         <f t="shared" si="3"/>
-        <v>-45512</v>
+        <v>14790</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.45">
@@ -4114,11 +4118,11 @@
         <v>4</v>
       </c>
       <c r="C245">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D245">
         <f t="shared" si="3"/>
-        <v>-45567</v>
+        <v>14758</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.45">
@@ -4129,11 +4133,11 @@
         <v>4</v>
       </c>
       <c r="C246">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D246">
         <f t="shared" si="3"/>
-        <v>-45577</v>
+        <v>14725</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.45">
@@ -4144,11 +4148,11 @@
         <v>4</v>
       </c>
       <c r="C247">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D247">
         <f t="shared" si="3"/>
-        <v>-45625</v>
+        <v>14628</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
@@ -4159,11 +4163,11 @@
         <v>4</v>
       </c>
       <c r="C248">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D248">
         <f t="shared" si="3"/>
-        <v>-45715</v>
+        <v>14588</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
@@ -4174,11 +4178,11 @@
         <v>4</v>
       </c>
       <c r="C249">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D249">
         <f t="shared" si="3"/>
-        <v>-45770</v>
+        <v>14538</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
@@ -4189,101 +4193,101 @@
         <v>4</v>
       </c>
       <c r="C250">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D250">
         <f t="shared" si="3"/>
-        <v>-45860</v>
+        <v>14488</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A251" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B251" t="s">
         <v>4</v>
       </c>
       <c r="C251">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D251">
         <f t="shared" si="3"/>
-        <v>-45910</v>
+        <v>14433</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A252" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B252" t="s">
         <v>4</v>
       </c>
       <c r="C252">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="D252">
         <f t="shared" si="3"/>
-        <v>-46011</v>
+        <v>14423</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B253" t="s">
         <v>4</v>
       </c>
       <c r="C253">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D253">
         <f t="shared" si="3"/>
-        <v>-46068</v>
+        <v>14375</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B254" t="s">
         <v>4</v>
       </c>
       <c r="C254">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D254">
         <f t="shared" si="3"/>
-        <v>-46088</v>
+        <v>14285</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A255" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B255" t="s">
         <v>4</v>
       </c>
       <c r="C255">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="D255">
         <f t="shared" si="3"/>
-        <v>-46201</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" s="1">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B256" t="s">
         <v>4</v>
       </c>
       <c r="C256">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D256">
         <f t="shared" si="3"/>
-        <v>-46266</v>
+        <v>14140</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
@@ -4294,226 +4298,226 @@
         <v>4</v>
       </c>
       <c r="C257">
-        <v>599</v>
+        <v>50</v>
       </c>
       <c r="D257">
         <f t="shared" si="3"/>
-        <v>-46865</v>
+        <v>14090</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" s="1">
-        <v>45477</v>
+        <v>45483</v>
       </c>
       <c r="B258" t="s">
         <v>4</v>
       </c>
       <c r="C258">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="D258">
         <f t="shared" si="3"/>
-        <v>-47195</v>
+        <v>13989</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" s="1">
-        <v>45477</v>
+        <v>45483</v>
       </c>
       <c r="B259" t="s">
         <v>4</v>
       </c>
       <c r="C259">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="D259">
         <f t="shared" si="3"/>
-        <v>-47410</v>
+        <v>13932</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" s="1">
-        <v>45463</v>
+        <v>45483</v>
       </c>
       <c r="B260" t="s">
         <v>4</v>
       </c>
       <c r="C260">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D260">
         <f t="shared" ref="D260:D323" si="4">IF(B260="Income",D259+C260,D259-C260)</f>
-        <v>-47506</v>
+        <v>13912</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A261" s="1">
-        <v>45463</v>
+        <v>45483</v>
       </c>
       <c r="B261" t="s">
         <v>4</v>
       </c>
       <c r="C261">
-        <v>275</v>
+        <v>113</v>
       </c>
       <c r="D261">
         <f t="shared" si="4"/>
-        <v>-47781</v>
+        <v>13799</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" s="1">
-        <v>45462</v>
+        <v>45483</v>
       </c>
       <c r="B262" t="s">
         <v>4</v>
       </c>
       <c r="C262">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D262">
         <f t="shared" si="4"/>
-        <v>-47881</v>
+        <v>13734</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" s="1">
-        <v>45462</v>
+        <v>45483</v>
       </c>
       <c r="B263" t="s">
         <v>4</v>
       </c>
       <c r="C263">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="D263">
         <f t="shared" si="4"/>
-        <v>-47961</v>
+        <v>13135</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A264" s="1">
-        <v>45462</v>
+        <v>45477</v>
       </c>
       <c r="B264" t="s">
         <v>4</v>
       </c>
       <c r="C264">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="D264">
         <f t="shared" si="4"/>
-        <v>-48071</v>
+        <v>12805</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" s="1">
-        <v>45461</v>
+        <v>45477</v>
       </c>
       <c r="B265" t="s">
         <v>4</v>
       </c>
       <c r="C265">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="D265">
         <f t="shared" si="4"/>
-        <v>-48171</v>
+        <v>12590</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A266" s="1">
-        <v>45461</v>
+        <v>45474</v>
       </c>
       <c r="B266" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C266">
-        <v>220</v>
+        <v>10000</v>
       </c>
       <c r="D266">
         <f t="shared" si="4"/>
-        <v>-48391</v>
+        <v>22590</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A267" s="1">
-        <v>45456</v>
+        <v>45463</v>
       </c>
       <c r="B267" t="s">
         <v>4</v>
       </c>
       <c r="C267">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D267">
         <f t="shared" si="4"/>
-        <v>-48471</v>
+        <v>22494</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" s="1">
-        <v>45456</v>
+        <v>45463</v>
       </c>
       <c r="B268" t="s">
         <v>4</v>
       </c>
       <c r="C268">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="D268">
         <f t="shared" si="4"/>
-        <v>-48526</v>
+        <v>22219</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A269" s="1">
-        <v>45455</v>
+        <v>45462</v>
       </c>
       <c r="B269" t="s">
         <v>4</v>
       </c>
       <c r="C269">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="D269">
         <f t="shared" si="4"/>
-        <v>-48569</v>
+        <v>22119</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" s="1">
-        <v>45455</v>
+        <v>45462</v>
       </c>
       <c r="B270" t="s">
         <v>4</v>
       </c>
       <c r="C270">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D270">
         <f t="shared" si="4"/>
-        <v>-48665</v>
+        <v>22039</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" s="1">
-        <v>45455</v>
+        <v>45462</v>
       </c>
       <c r="B271" t="s">
         <v>4</v>
       </c>
       <c r="C271">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D271">
         <f t="shared" si="4"/>
-        <v>-48785</v>
+        <v>21929</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A272" s="1">
-        <v>45454</v>
+        <v>45461</v>
       </c>
       <c r="B272" t="s">
         <v>4</v>
@@ -4523,117 +4527,117 @@
       </c>
       <c r="D272">
         <f t="shared" si="4"/>
-        <v>-48885</v>
+        <v>21829</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" s="1">
-        <v>45454</v>
+        <v>45461</v>
       </c>
       <c r="B273" t="s">
         <v>4</v>
       </c>
       <c r="C273">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="D273">
         <f t="shared" si="4"/>
-        <v>-48995</v>
+        <v>21609</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A274" s="1">
-        <v>45450</v>
+        <v>45456</v>
       </c>
       <c r="B274" t="s">
         <v>4</v>
       </c>
       <c r="C274">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D274">
         <f t="shared" si="4"/>
-        <v>-49045</v>
+        <v>21529</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A275" s="1">
-        <v>45450</v>
+        <v>45456</v>
       </c>
       <c r="B275" t="s">
         <v>4</v>
       </c>
       <c r="C275">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D275">
         <f t="shared" si="4"/>
-        <v>-49105</v>
+        <v>21474</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A276" s="1">
-        <v>45448</v>
+        <v>45455</v>
       </c>
       <c r="B276" t="s">
         <v>4</v>
       </c>
       <c r="C276">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="D276">
         <f t="shared" si="4"/>
-        <v>-49205</v>
+        <v>21431</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" s="1">
-        <v>45448</v>
+        <v>45455</v>
       </c>
       <c r="B277" t="s">
         <v>4</v>
       </c>
       <c r="C277">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D277">
         <f t="shared" si="4"/>
-        <v>-49270</v>
+        <v>21335</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A278" s="1">
-        <v>45448</v>
+        <v>45455</v>
       </c>
       <c r="B278" t="s">
         <v>4</v>
       </c>
       <c r="C278">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="D278">
         <f t="shared" si="4"/>
-        <v>-49460</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A279" s="1">
-        <v>45448</v>
+        <v>45454</v>
       </c>
       <c r="B279" t="s">
         <v>4</v>
       </c>
       <c r="C279">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D279">
         <f t="shared" si="4"/>
-        <v>-49500</v>
+        <v>21115</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" s="1">
-        <v>45448</v>
+        <v>45454</v>
       </c>
       <c r="B280" t="s">
         <v>4</v>
@@ -4643,1467 +4647,1467 @@
       </c>
       <c r="D280">
         <f t="shared" si="4"/>
-        <v>-49610</v>
+        <v>21005</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" s="1">
-        <v>45447</v>
+        <v>45450</v>
       </c>
       <c r="B281" t="s">
         <v>4</v>
       </c>
       <c r="C281">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D281">
         <f t="shared" si="4"/>
-        <v>-49700</v>
+        <v>20955</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A282" s="1">
-        <v>45447</v>
+        <v>45450</v>
       </c>
       <c r="B282" t="s">
         <v>4</v>
       </c>
       <c r="C282">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D282">
         <f t="shared" si="4"/>
-        <v>-49770</v>
+        <v>20895</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A283" s="1">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="B283" t="s">
         <v>4</v>
       </c>
       <c r="C283">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D283">
         <f t="shared" si="4"/>
-        <v>-49880</v>
+        <v>20795</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A284" s="1">
-        <v>45446</v>
+        <v>45448</v>
       </c>
       <c r="B284" t="s">
         <v>4</v>
       </c>
       <c r="C284">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D284">
         <f t="shared" si="4"/>
-        <v>-49955</v>
+        <v>20730</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A285" s="1">
-        <v>45445</v>
+        <v>45448</v>
       </c>
       <c r="B285" t="s">
         <v>4</v>
       </c>
       <c r="C285">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="D285">
         <f t="shared" si="4"/>
-        <v>-50010</v>
+        <v>20540</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" s="1">
-        <v>45445</v>
+        <v>45448</v>
       </c>
       <c r="B286" t="s">
         <v>4</v>
       </c>
       <c r="C286">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="D286">
         <f t="shared" si="4"/>
-        <v>-50188</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A287" s="1">
-        <v>45445</v>
+        <v>45448</v>
       </c>
       <c r="B287" t="s">
         <v>4</v>
       </c>
       <c r="C287">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D287">
         <f t="shared" si="4"/>
-        <v>-50284</v>
+        <v>20390</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A288" s="1">
-        <v>45444</v>
+        <v>45447</v>
       </c>
       <c r="B288" t="s">
         <v>4</v>
       </c>
       <c r="C288">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="D288">
         <f t="shared" si="4"/>
-        <v>-50484</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" s="1">
-        <v>45444</v>
+        <v>45447</v>
       </c>
       <c r="B289" t="s">
         <v>4</v>
       </c>
       <c r="C289">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D289">
         <f t="shared" si="4"/>
-        <v>-50571</v>
+        <v>20230</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A290" s="1">
-        <v>45444</v>
+        <v>45447</v>
       </c>
       <c r="B290" t="s">
         <v>4</v>
       </c>
       <c r="C290">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D290">
         <f t="shared" si="4"/>
-        <v>-50621</v>
+        <v>20120</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" s="1">
-        <v>45444</v>
+        <v>45446</v>
       </c>
       <c r="B291" t="s">
         <v>4</v>
       </c>
       <c r="C291">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D291">
         <f t="shared" si="4"/>
-        <v>-50672</v>
+        <v>20045</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A292" s="1">
-        <v>45443</v>
+        <v>45445</v>
       </c>
       <c r="B292" t="s">
         <v>4</v>
       </c>
       <c r="C292">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="D292">
         <f t="shared" si="4"/>
-        <v>-50886</v>
+        <v>19990</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A293" s="1">
-        <v>45442</v>
+        <v>45445</v>
       </c>
       <c r="B293" t="s">
         <v>4</v>
       </c>
       <c r="C293">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="D293">
         <f t="shared" si="4"/>
-        <v>-50986</v>
+        <v>19812</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A294" s="1">
-        <v>45442</v>
+        <v>45445</v>
       </c>
       <c r="B294" t="s">
         <v>4</v>
       </c>
       <c r="C294">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D294">
         <f t="shared" si="4"/>
-        <v>-51046</v>
+        <v>19716</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" s="1">
-        <v>45442</v>
+        <v>45444</v>
       </c>
       <c r="B295" t="s">
         <v>4</v>
       </c>
       <c r="C295">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D295">
         <f t="shared" si="4"/>
-        <v>-51228</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A296" s="1">
-        <v>45441</v>
+        <v>45444</v>
       </c>
       <c r="B296" t="s">
         <v>4</v>
       </c>
       <c r="C296">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="D296">
         <f t="shared" si="4"/>
-        <v>-51338</v>
+        <v>19429</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" s="1">
-        <v>45441</v>
+        <v>45444</v>
       </c>
       <c r="B297" t="s">
         <v>4</v>
       </c>
       <c r="C297">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D297">
         <f t="shared" si="4"/>
-        <v>-51398</v>
+        <v>19379</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" s="1">
-        <v>45441</v>
+        <v>45444</v>
       </c>
       <c r="B298" t="s">
         <v>4</v>
       </c>
       <c r="C298">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="D298">
         <f t="shared" si="4"/>
-        <v>-51523</v>
+        <v>19328</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" s="1">
-        <v>45440</v>
+        <v>45444</v>
       </c>
       <c r="B299" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C299">
-        <v>50</v>
+        <v>10000</v>
       </c>
       <c r="D299">
         <f t="shared" si="4"/>
-        <v>-51573</v>
+        <v>29328</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A300" s="1">
-        <v>45440</v>
+        <v>45443</v>
       </c>
       <c r="B300" t="s">
         <v>4</v>
       </c>
       <c r="C300">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="D300">
         <f t="shared" si="4"/>
-        <v>-51677</v>
+        <v>29114</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A301" s="1">
-        <v>45440</v>
+        <v>45442</v>
       </c>
       <c r="B301" t="s">
         <v>4</v>
       </c>
       <c r="C301">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D301">
         <f t="shared" si="4"/>
-        <v>-51787</v>
+        <v>29014</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A302" s="1">
-        <v>45440</v>
+        <v>45442</v>
       </c>
       <c r="B302" t="s">
         <v>4</v>
       </c>
       <c r="C302">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D302">
         <f t="shared" si="4"/>
-        <v>-51886</v>
+        <v>28954</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A303" s="1">
-        <v>45439</v>
+        <v>45442</v>
       </c>
       <c r="B303" t="s">
         <v>4</v>
       </c>
       <c r="C303">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="D303">
         <f t="shared" si="4"/>
-        <v>-52000</v>
+        <v>28772</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" s="1">
-        <v>45439</v>
+        <v>45441</v>
       </c>
       <c r="B304" t="s">
         <v>4</v>
       </c>
       <c r="C304">
-        <v>1500</v>
+        <v>110</v>
       </c>
       <c r="D304">
         <f t="shared" si="4"/>
-        <v>-53500</v>
+        <v>28662</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" s="1">
-        <v>45436</v>
+        <v>45441</v>
       </c>
       <c r="B305" t="s">
         <v>4</v>
       </c>
       <c r="C305">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="D305">
         <f t="shared" si="4"/>
-        <v>-53776</v>
+        <v>28602</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A306" s="1">
-        <v>45435</v>
+        <v>45441</v>
       </c>
       <c r="B306" t="s">
         <v>4</v>
       </c>
       <c r="C306">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D306">
         <f t="shared" si="4"/>
-        <v>-53916</v>
+        <v>28477</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" s="1">
-        <v>45435</v>
+        <v>45440</v>
       </c>
       <c r="B307" t="s">
         <v>4</v>
       </c>
       <c r="C307">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="D307">
         <f t="shared" si="4"/>
-        <v>-54186</v>
+        <v>28427</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" s="1">
-        <v>45435</v>
+        <v>45440</v>
       </c>
       <c r="B308" t="s">
         <v>4</v>
       </c>
       <c r="C308">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="D308">
         <f t="shared" si="4"/>
-        <v>-54211</v>
+        <v>28323</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" s="1">
-        <v>45435</v>
+        <v>45440</v>
       </c>
       <c r="B309" t="s">
         <v>4</v>
       </c>
       <c r="C309">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="D309">
         <f t="shared" si="4"/>
-        <v>-54421</v>
+        <v>28213</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" s="1">
-        <v>45434</v>
+        <v>45440</v>
       </c>
       <c r="B310" t="s">
         <v>4</v>
       </c>
       <c r="C310">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D310">
         <f t="shared" si="4"/>
-        <v>-54521</v>
+        <v>28114</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" s="1">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="B311" t="s">
         <v>4</v>
       </c>
       <c r="C311">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="D311">
         <f t="shared" si="4"/>
-        <v>-54566</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="1">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="B312" t="s">
         <v>4</v>
       </c>
       <c r="C312">
-        <v>55</v>
+        <v>1500</v>
       </c>
       <c r="D312">
         <f t="shared" si="4"/>
-        <v>-54621</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1">
-        <v>45434</v>
+        <v>45436</v>
       </c>
       <c r="B313" t="s">
         <v>4</v>
       </c>
       <c r="C313">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="D313">
         <f t="shared" si="4"/>
-        <v>-54717</v>
+        <v>26224</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="B314" t="s">
         <v>4</v>
       </c>
       <c r="C314">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="D314">
         <f t="shared" si="4"/>
-        <v>-54737</v>
+        <v>26084</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="B315" t="s">
         <v>4</v>
       </c>
       <c r="C315">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="D315">
         <f t="shared" si="4"/>
-        <v>-54851</v>
+        <v>25814</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" s="1">
-        <v>45432</v>
+        <v>45435</v>
       </c>
       <c r="B316" t="s">
         <v>4</v>
       </c>
       <c r="C316">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D316">
         <f t="shared" si="4"/>
-        <v>-54921</v>
+        <v>25789</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1">
-        <v>45432</v>
+        <v>45435</v>
       </c>
       <c r="B317" t="s">
         <v>4</v>
       </c>
       <c r="C317">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="D317">
         <f t="shared" si="4"/>
-        <v>-55201</v>
+        <v>25579</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1">
-        <v>45431</v>
+        <v>45434</v>
       </c>
       <c r="B318" t="s">
         <v>4</v>
       </c>
       <c r="C318">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D318">
         <f t="shared" si="4"/>
-        <v>-55291</v>
+        <v>25479</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1">
-        <v>45431</v>
+        <v>45434</v>
       </c>
       <c r="B319" t="s">
         <v>4</v>
       </c>
       <c r="C319">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="D319">
         <f t="shared" si="4"/>
-        <v>-55449</v>
+        <v>25434</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" s="1">
-        <v>45431</v>
+        <v>45434</v>
       </c>
       <c r="B320" t="s">
         <v>4</v>
       </c>
       <c r="C320">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D320">
         <f t="shared" si="4"/>
-        <v>-55519</v>
+        <v>25379</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" s="1">
-        <v>45431</v>
+        <v>45434</v>
       </c>
       <c r="B321" t="s">
         <v>4</v>
       </c>
       <c r="C321">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="D321">
         <f t="shared" si="4"/>
-        <v>-55544</v>
+        <v>25283</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" s="1">
-        <v>45431</v>
+        <v>45433</v>
       </c>
       <c r="B322" t="s">
         <v>4</v>
       </c>
       <c r="C322">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="D322">
         <f t="shared" si="4"/>
-        <v>-55812</v>
+        <v>25263</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A323" s="1">
-        <v>45429</v>
+        <v>45433</v>
       </c>
       <c r="B323" t="s">
         <v>4</v>
       </c>
       <c r="C323">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="D323">
         <f t="shared" si="4"/>
-        <v>-56022</v>
+        <v>25149</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A324" s="1">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="B324" t="s">
         <v>4</v>
       </c>
       <c r="C324">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D324">
         <f t="shared" ref="D324:D387" si="5">IF(B324="Income",D323+C324,D323-C324)</f>
-        <v>-56039</v>
+        <v>25079</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" s="1">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="B325" t="s">
         <v>4</v>
       </c>
       <c r="C325">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="D325">
         <f t="shared" si="5"/>
-        <v>-56209</v>
+        <v>24799</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A326" s="1">
-        <v>45428</v>
+        <v>45431</v>
       </c>
       <c r="B326" t="s">
         <v>4</v>
       </c>
       <c r="C326">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="D326">
         <f t="shared" si="5"/>
-        <v>-56334</v>
+        <v>24709</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A327" s="1">
-        <v>45428</v>
+        <v>45431</v>
       </c>
       <c r="B327" t="s">
         <v>4</v>
       </c>
       <c r="C327">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="D327">
         <f t="shared" si="5"/>
-        <v>-56384</v>
+        <v>24551</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A328" s="1">
-        <v>45428</v>
+        <v>45431</v>
       </c>
       <c r="B328" t="s">
         <v>4</v>
       </c>
       <c r="C328">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="D328">
         <f t="shared" si="5"/>
-        <v>-56502</v>
+        <v>24481</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" s="1">
-        <v>45427</v>
+        <v>45431</v>
       </c>
       <c r="B329" t="s">
         <v>4</v>
       </c>
       <c r="C329">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D329">
         <f t="shared" si="5"/>
-        <v>-56519</v>
+        <v>24456</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A330" s="1">
-        <v>45427</v>
+        <v>45431</v>
       </c>
       <c r="B330" t="s">
         <v>4</v>
       </c>
       <c r="C330">
-        <v>114</v>
+        <v>268</v>
       </c>
       <c r="D330">
         <f t="shared" si="5"/>
-        <v>-56633</v>
+        <v>24188</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" s="1">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="B331" t="s">
         <v>4</v>
       </c>
       <c r="C331">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="D331">
         <f t="shared" si="5"/>
-        <v>-56753</v>
+        <v>23978</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A332" s="1">
-        <v>45426</v>
+        <v>45429</v>
       </c>
       <c r="B332" t="s">
         <v>4</v>
       </c>
       <c r="C332">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="D332">
         <f t="shared" si="5"/>
-        <v>-56868</v>
+        <v>23961</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A333" s="1">
-        <v>45426</v>
+        <v>45429</v>
       </c>
       <c r="B333" t="s">
         <v>4</v>
       </c>
       <c r="C333">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D333">
         <f t="shared" si="5"/>
-        <v>-56998</v>
+        <v>23791</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" s="1">
-        <v>45425</v>
+        <v>45428</v>
       </c>
       <c r="B334" t="s">
         <v>4</v>
       </c>
       <c r="C334">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="D334">
         <f t="shared" si="5"/>
-        <v>-57038</v>
+        <v>23666</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A335" s="1">
-        <v>45425</v>
+        <v>45428</v>
       </c>
       <c r="B335" t="s">
         <v>4</v>
       </c>
       <c r="C335">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D335">
         <f t="shared" si="5"/>
-        <v>-57538</v>
+        <v>23616</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A336" s="1">
-        <v>45422</v>
+        <v>45428</v>
       </c>
       <c r="B336" t="s">
         <v>4</v>
       </c>
       <c r="C336">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D336">
         <f t="shared" si="5"/>
-        <v>-57618</v>
+        <v>23498</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" s="1">
-        <v>45422</v>
+        <v>45427</v>
       </c>
       <c r="B337" t="s">
         <v>4</v>
       </c>
       <c r="C337">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D337">
         <f t="shared" si="5"/>
-        <v>-57638</v>
+        <v>23481</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A338" s="1">
-        <v>45421</v>
+        <v>45427</v>
       </c>
       <c r="B338" t="s">
         <v>4</v>
       </c>
       <c r="C338">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D338">
         <f t="shared" si="5"/>
-        <v>-57765</v>
+        <v>23367</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A339" s="1">
-        <v>45421</v>
+        <v>45427</v>
       </c>
       <c r="B339" t="s">
         <v>4</v>
       </c>
       <c r="C339">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D339">
         <f t="shared" si="5"/>
-        <v>-57835</v>
+        <v>23247</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" s="1">
-        <v>45421</v>
+        <v>45426</v>
       </c>
       <c r="B340" t="s">
         <v>4</v>
       </c>
       <c r="C340">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D340">
         <f t="shared" si="5"/>
-        <v>-57920</v>
+        <v>23132</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A341" s="1">
-        <v>45421</v>
+        <v>45426</v>
       </c>
       <c r="B341" t="s">
         <v>4</v>
       </c>
       <c r="C341">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="D341">
         <f t="shared" si="5"/>
-        <v>-57965</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A342" s="1">
-        <v>45421</v>
+        <v>45425</v>
       </c>
       <c r="B342" t="s">
         <v>4</v>
       </c>
       <c r="C342">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="D342">
         <f t="shared" si="5"/>
-        <v>-58075</v>
+        <v>22962</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" s="1">
-        <v>45420</v>
+        <v>45425</v>
       </c>
       <c r="B343" t="s">
         <v>4</v>
       </c>
       <c r="C343">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="D343">
         <f t="shared" si="5"/>
-        <v>-58130</v>
+        <v>22462</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A344" s="1">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="B344" t="s">
         <v>4</v>
       </c>
       <c r="C344">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D344">
         <f t="shared" si="5"/>
-        <v>-58220</v>
+        <v>22382</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" s="1">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="B345" t="s">
         <v>4</v>
       </c>
       <c r="C345">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D345">
         <f t="shared" si="5"/>
-        <v>-58316</v>
+        <v>22362</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" s="1">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="B346" t="s">
         <v>4</v>
       </c>
       <c r="C346">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="D346">
         <f t="shared" si="5"/>
-        <v>-58365</v>
+        <v>22235</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" s="1">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="B347" t="s">
         <v>4</v>
       </c>
       <c r="C347">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D347">
         <f t="shared" si="5"/>
-        <v>-58415</v>
+        <v>22165</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A348" s="1">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="B348" t="s">
         <v>4</v>
       </c>
       <c r="C348">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="D348">
         <f t="shared" si="5"/>
-        <v>-58540</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" s="1">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="B349" t="s">
         <v>4</v>
       </c>
       <c r="C349">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D349">
         <f t="shared" si="5"/>
-        <v>-58565</v>
+        <v>22035</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A350" s="1">
-        <v>45418</v>
+        <v>45421</v>
       </c>
       <c r="B350" t="s">
         <v>4</v>
       </c>
       <c r="C350">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D350">
         <f t="shared" si="5"/>
-        <v>-58665</v>
+        <v>21925</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A351" s="1">
-        <v>45418</v>
+        <v>45420</v>
       </c>
       <c r="B351" t="s">
         <v>4</v>
       </c>
       <c r="C351">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="D351">
         <f t="shared" si="5"/>
-        <v>-58915</v>
+        <v>21870</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" s="1">
-        <v>45415</v>
+        <v>45420</v>
       </c>
       <c r="B352" t="s">
         <v>4</v>
       </c>
       <c r="C352">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D352">
         <f t="shared" si="5"/>
-        <v>-59015</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" s="1">
-        <v>45415</v>
+        <v>45420</v>
       </c>
       <c r="B353" t="s">
         <v>4</v>
       </c>
       <c r="C353">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D353">
         <f t="shared" si="5"/>
-        <v>-59115</v>
+        <v>21684</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A354" s="1">
-        <v>45415</v>
+        <v>45419</v>
       </c>
       <c r="B354" t="s">
         <v>4</v>
       </c>
       <c r="C354">
-        <v>330</v>
+        <v>49</v>
       </c>
       <c r="D354">
         <f t="shared" si="5"/>
-        <v>-59445</v>
+        <v>21635</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" s="1">
-        <v>45415</v>
+        <v>45419</v>
       </c>
       <c r="B355" t="s">
         <v>4</v>
       </c>
       <c r="C355">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D355">
         <f t="shared" si="5"/>
-        <v>-59545</v>
+        <v>21585</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A356" s="1">
-        <v>45414</v>
+        <v>45419</v>
       </c>
       <c r="B356" t="s">
         <v>4</v>
       </c>
       <c r="C356">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D356">
         <f t="shared" si="5"/>
-        <v>-59660</v>
+        <v>21460</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A357" s="1">
-        <v>45414</v>
+        <v>45419</v>
       </c>
       <c r="B357" t="s">
         <v>4</v>
       </c>
       <c r="C357">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="D357">
         <f t="shared" si="5"/>
-        <v>-59813</v>
+        <v>21435</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" s="1">
-        <v>45413</v>
+        <v>45418</v>
       </c>
       <c r="B358" t="s">
         <v>4</v>
       </c>
       <c r="C358">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D358">
         <f t="shared" si="5"/>
-        <v>-59858</v>
+        <v>21335</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" s="1">
-        <v>45413</v>
+        <v>45418</v>
       </c>
       <c r="B359" t="s">
         <v>4</v>
       </c>
       <c r="C359">
-        <v>124</v>
+        <v>250</v>
       </c>
       <c r="D359">
         <f t="shared" si="5"/>
-        <v>-59982</v>
+        <v>21085</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" s="1">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="B360" t="s">
         <v>4</v>
       </c>
       <c r="C360">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D360">
         <f t="shared" si="5"/>
-        <v>-60182</v>
+        <v>20985</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" s="1">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="B361" t="s">
         <v>4</v>
       </c>
       <c r="C361">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D361">
         <f t="shared" si="5"/>
-        <v>-60582</v>
+        <v>20885</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A362" s="1">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="B362" t="s">
         <v>4</v>
       </c>
       <c r="C362">
-        <v>22</v>
+        <v>330</v>
       </c>
       <c r="D362">
         <f t="shared" si="5"/>
-        <v>-60604</v>
+        <v>20555</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" s="1">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="B363" t="s">
         <v>4</v>
       </c>
       <c r="C363">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D363">
         <f t="shared" si="5"/>
-        <v>-60687</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" s="1">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="B364" t="s">
         <v>4</v>
       </c>
       <c r="C364">
-        <v>290</v>
+        <v>115</v>
       </c>
       <c r="D364">
         <f t="shared" si="5"/>
-        <v>-60977</v>
+        <v>20340</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A365" s="1">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="B365" t="s">
         <v>4</v>
       </c>
       <c r="C365">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D365">
         <f t="shared" si="5"/>
-        <v>-61127</v>
+        <v>20187</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A366" s="1">
-        <v>45411</v>
+        <v>45413</v>
       </c>
       <c r="B366" t="s">
         <v>4</v>
       </c>
       <c r="C366">
-        <v>330</v>
+        <v>45</v>
       </c>
       <c r="D366">
         <f t="shared" si="5"/>
-        <v>-61457</v>
+        <v>20142</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" s="1">
-        <v>45411</v>
+        <v>45413</v>
       </c>
       <c r="B367" t="s">
         <v>4</v>
       </c>
       <c r="C367">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="D367">
         <f t="shared" si="5"/>
-        <v>-61627</v>
+        <v>20018</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A368" s="1">
-        <v>45411</v>
+        <v>45413</v>
       </c>
       <c r="B368" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C368">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="D368">
         <f t="shared" si="5"/>
-        <v>-61727</v>
+        <v>30018</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" s="1">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="B369" t="s">
         <v>4</v>
       </c>
       <c r="C369">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D369">
         <f t="shared" si="5"/>
-        <v>-61827</v>
+        <v>29818</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" s="1">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="B370" t="s">
         <v>4</v>
       </c>
       <c r="C370">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="D370">
         <f t="shared" si="5"/>
-        <v>-61877</v>
+        <v>29418</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" s="1">
-        <v>45406</v>
+        <v>45412</v>
       </c>
       <c r="B371" t="s">
         <v>4</v>
       </c>
       <c r="C371">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="D371">
         <f t="shared" si="5"/>
-        <v>-61973</v>
+        <v>29396</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" s="1">
-        <v>45406</v>
+        <v>45412</v>
       </c>
       <c r="B372" t="s">
         <v>4</v>
       </c>
       <c r="C372">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D372">
         <f t="shared" si="5"/>
-        <v>-62073</v>
+        <v>29313</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" s="1">
-        <v>45405</v>
+        <v>45411</v>
       </c>
       <c r="B373" t="s">
         <v>4</v>
       </c>
       <c r="C373">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="D373">
         <f t="shared" si="5"/>
-        <v>-62103</v>
+        <v>29023</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A374" s="1">
-        <v>45405</v>
+        <v>45411</v>
       </c>
       <c r="B374" t="s">
         <v>4</v>
       </c>
       <c r="C374">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D374">
         <f t="shared" si="5"/>
-        <v>-62203</v>
+        <v>28873</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A375" s="1">
-        <v>45405</v>
+        <v>45411</v>
       </c>
       <c r="B375" t="s">
         <v>4</v>
       </c>
       <c r="C375">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="D375">
         <f t="shared" si="5"/>
-        <v>-62298</v>
+        <v>28543</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" s="1">
-        <v>45404</v>
+        <v>45411</v>
       </c>
       <c r="B376" t="s">
         <v>4</v>
       </c>
       <c r="C376">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="D376">
         <f t="shared" si="5"/>
-        <v>-62398</v>
+        <v>28373</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" s="1">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="B377" t="s">
         <v>4</v>
       </c>
       <c r="C377">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D377">
         <f t="shared" si="5"/>
-        <v>-62423</v>
+        <v>28273</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A378" s="1">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="B378" t="s">
         <v>4</v>
@@ -6113,1497 +6117,1497 @@
       </c>
       <c r="D378">
         <f t="shared" si="5"/>
-        <v>-62523</v>
+        <v>28173</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" s="1">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="B379" t="s">
         <v>4</v>
       </c>
       <c r="C379">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="D379">
         <f t="shared" si="5"/>
-        <v>-62853</v>
+        <v>28123</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A380" s="1">
-        <v>45401</v>
+        <v>45406</v>
       </c>
       <c r="B380" t="s">
         <v>4</v>
       </c>
       <c r="C380">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D380">
         <f t="shared" si="5"/>
-        <v>-62953</v>
+        <v>28027</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A381" s="1">
-        <v>45401</v>
+        <v>45406</v>
       </c>
       <c r="B381" t="s">
         <v>4</v>
       </c>
       <c r="C381">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="D381">
         <f t="shared" si="5"/>
-        <v>-63286</v>
+        <v>27927</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" s="1">
-        <v>45400</v>
+        <v>45405</v>
       </c>
       <c r="B382" t="s">
         <v>4</v>
       </c>
       <c r="C382">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D382">
         <f t="shared" si="5"/>
-        <v>-63301</v>
+        <v>27897</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A383" s="1">
-        <v>45400</v>
+        <v>45405</v>
       </c>
       <c r="B383" t="s">
         <v>4</v>
       </c>
       <c r="C383">
-        <v>588</v>
+        <v>100</v>
       </c>
       <c r="D383">
         <f t="shared" si="5"/>
-        <v>-63889</v>
+        <v>27797</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A384" s="1">
-        <v>45400</v>
+        <v>45405</v>
       </c>
       <c r="B384" t="s">
         <v>4</v>
       </c>
       <c r="C384">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D384">
         <f t="shared" si="5"/>
-        <v>-63974</v>
+        <v>27702</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" s="1">
-        <v>45400</v>
+        <v>45404</v>
       </c>
       <c r="B385" t="s">
         <v>4</v>
       </c>
       <c r="C385">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D385">
         <f t="shared" si="5"/>
-        <v>-64054</v>
+        <v>27602</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A386" s="1">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="B386" t="s">
         <v>4</v>
       </c>
       <c r="C386">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="D386">
         <f t="shared" si="5"/>
-        <v>-64139</v>
+        <v>27577</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A387" s="1">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="B387" t="s">
         <v>4</v>
       </c>
       <c r="C387">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D387">
         <f t="shared" si="5"/>
-        <v>-64209</v>
+        <v>27477</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" s="1">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="B388" t="s">
         <v>4</v>
       </c>
       <c r="C388">
-        <v>88</v>
+        <v>330</v>
       </c>
       <c r="D388">
         <f t="shared" ref="D388:D451" si="6">IF(B388="Income",D387+C388,D387-C388)</f>
-        <v>-64297</v>
+        <v>27147</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A389" s="1">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="B389" t="s">
         <v>4</v>
       </c>
       <c r="C389">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D389">
         <f t="shared" si="6"/>
-        <v>-64342</v>
+        <v>27047</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A390" s="1">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="B390" t="s">
         <v>4</v>
       </c>
       <c r="C390">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="D390">
         <f t="shared" si="6"/>
-        <v>-64427</v>
+        <v>26714</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A391" s="1">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="B391" t="s">
         <v>4</v>
       </c>
       <c r="C391">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="D391">
         <f t="shared" si="6"/>
-        <v>-64537</v>
+        <v>26699</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A392" s="1">
-        <v>45395</v>
+        <v>45400</v>
       </c>
       <c r="B392" t="s">
         <v>4</v>
       </c>
       <c r="C392">
-        <v>350</v>
+        <v>588</v>
       </c>
       <c r="D392">
         <f t="shared" si="6"/>
-        <v>-64887</v>
+        <v>26111</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" s="1">
-        <v>45395</v>
+        <v>45400</v>
       </c>
       <c r="B393" t="s">
         <v>4</v>
       </c>
       <c r="C393">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D393">
         <f t="shared" si="6"/>
-        <v>-65007</v>
+        <v>26026</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" s="1">
-        <v>45395</v>
+        <v>45400</v>
       </c>
       <c r="B394" t="s">
         <v>4</v>
       </c>
       <c r="C394">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D394">
         <f t="shared" si="6"/>
-        <v>-65107</v>
+        <v>25946</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" s="1">
-        <v>45394</v>
+        <v>45399</v>
       </c>
       <c r="B395" t="s">
         <v>4</v>
       </c>
       <c r="C395">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D395">
         <f t="shared" si="6"/>
-        <v>-65217</v>
+        <v>25861</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A396" s="1">
-        <v>45393</v>
+        <v>45399</v>
       </c>
       <c r="B396" t="s">
         <v>4</v>
       </c>
       <c r="C396">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D396">
         <f t="shared" si="6"/>
-        <v>-65357</v>
+        <v>25791</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" s="1">
-        <v>45393</v>
+        <v>45399</v>
       </c>
       <c r="B397" t="s">
         <v>4</v>
       </c>
       <c r="C397">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="D397">
         <f t="shared" si="6"/>
-        <v>-65509</v>
+        <v>25703</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A398" s="1">
-        <v>45392</v>
+        <v>45398</v>
       </c>
       <c r="B398" t="s">
         <v>4</v>
       </c>
       <c r="C398">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D398">
         <f t="shared" si="6"/>
-        <v>-65609</v>
+        <v>25658</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A399" s="1">
-        <v>45392</v>
+        <v>45398</v>
       </c>
       <c r="B399" t="s">
         <v>4</v>
       </c>
       <c r="C399">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c r="D399">
         <f t="shared" si="6"/>
-        <v>-65857</v>
+        <v>25573</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" s="1">
-        <v>45392</v>
+        <v>45398</v>
       </c>
       <c r="B400" t="s">
         <v>4</v>
       </c>
       <c r="C400">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D400">
         <f t="shared" si="6"/>
-        <v>-65953</v>
+        <v>25463</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" s="1">
-        <v>45391</v>
+        <v>45395</v>
       </c>
       <c r="B401" t="s">
         <v>4</v>
       </c>
       <c r="C401">
-        <v>25</v>
+        <v>350</v>
       </c>
       <c r="D401">
         <f t="shared" si="6"/>
-        <v>-65978</v>
+        <v>25113</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A402" s="1">
-        <v>45391</v>
+        <v>45395</v>
       </c>
       <c r="B402" t="s">
         <v>4</v>
       </c>
       <c r="C402">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D402">
         <f t="shared" si="6"/>
-        <v>-66088</v>
+        <v>24993</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" s="1">
-        <v>45391</v>
+        <v>45395</v>
       </c>
       <c r="B403" t="s">
         <v>4</v>
       </c>
       <c r="C403">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D403">
         <f t="shared" si="6"/>
-        <v>-66198</v>
+        <v>24893</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A404" s="1">
-        <v>45391</v>
+        <v>45394</v>
       </c>
       <c r="B404" t="s">
         <v>4</v>
       </c>
       <c r="C404">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D404">
         <f t="shared" si="6"/>
-        <v>-66248</v>
+        <v>24783</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A405" s="1">
-        <v>45387</v>
+        <v>45393</v>
       </c>
       <c r="B405" t="s">
         <v>4</v>
       </c>
       <c r="C405">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="D405">
         <f t="shared" si="6"/>
-        <v>-66298</v>
+        <v>24643</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" s="1">
-        <v>45386</v>
+        <v>45393</v>
       </c>
       <c r="B406" t="s">
         <v>4</v>
       </c>
       <c r="C406">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="D406">
         <f t="shared" si="6"/>
-        <v>-66328</v>
+        <v>24491</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A407" s="1">
-        <v>45386</v>
+        <v>45392</v>
       </c>
       <c r="B407" t="s">
         <v>4</v>
       </c>
       <c r="C407">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D407">
         <f t="shared" si="6"/>
-        <v>-66363</v>
+        <v>24391</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A408" s="1">
-        <v>45386</v>
+        <v>45392</v>
       </c>
       <c r="B408" t="s">
         <v>4</v>
       </c>
       <c r="C408">
-        <v>45</v>
+        <v>248</v>
       </c>
       <c r="D408">
         <f t="shared" si="6"/>
-        <v>-66408</v>
+        <v>24143</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" s="1">
-        <v>45386</v>
+        <v>45392</v>
       </c>
       <c r="B409" t="s">
         <v>4</v>
       </c>
       <c r="C409">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="D409">
         <f t="shared" si="6"/>
-        <v>-66608</v>
+        <v>24047</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A410" s="1">
-        <v>45386</v>
+        <v>45391</v>
       </c>
       <c r="B410" t="s">
         <v>4</v>
       </c>
       <c r="C410">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="D410">
         <f t="shared" si="6"/>
-        <v>-66908</v>
+        <v>24022</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A411" s="1">
-        <v>45384</v>
+        <v>45391</v>
       </c>
       <c r="B411" t="s">
         <v>4</v>
       </c>
       <c r="C411">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D411">
         <f t="shared" si="6"/>
-        <v>-67038</v>
+        <v>23912</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" s="1">
-        <v>45384</v>
+        <v>45391</v>
       </c>
       <c r="B412" t="s">
         <v>4</v>
       </c>
       <c r="C412">
-        <v>430</v>
+        <v>110</v>
       </c>
       <c r="D412">
         <f t="shared" si="6"/>
-        <v>-67468</v>
+        <v>23802</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A413" s="1">
-        <v>45384</v>
+        <v>45391</v>
       </c>
       <c r="B413" t="s">
         <v>4</v>
       </c>
       <c r="C413">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D413">
         <f t="shared" si="6"/>
-        <v>-67588</v>
+        <v>23752</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A414" s="1">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="B414" t="s">
         <v>4</v>
       </c>
       <c r="C414">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="D414">
         <f t="shared" si="6"/>
-        <v>-67684</v>
+        <v>23702</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" s="1">
-        <v>45384</v>
+        <v>45386</v>
       </c>
       <c r="B415" t="s">
         <v>4</v>
       </c>
       <c r="C415">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D415">
         <f t="shared" si="6"/>
-        <v>-67794</v>
+        <v>23672</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A416" s="1">
-        <v>45380</v>
+        <v>45386</v>
       </c>
       <c r="B416" t="s">
         <v>4</v>
       </c>
       <c r="C416">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D416">
         <f t="shared" si="6"/>
-        <v>-67844</v>
+        <v>23637</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" s="1">
-        <v>45380</v>
+        <v>45386</v>
       </c>
       <c r="B417" t="s">
         <v>4</v>
       </c>
       <c r="C417">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="D417">
         <f t="shared" si="6"/>
-        <v>-67954</v>
+        <v>23592</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" s="1">
-        <v>45379</v>
+        <v>45386</v>
       </c>
       <c r="B418" t="s">
         <v>4</v>
       </c>
       <c r="C418">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D418">
         <f t="shared" si="6"/>
-        <v>-68054</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A419" s="1">
-        <v>45379</v>
+        <v>45386</v>
       </c>
       <c r="B419" t="s">
         <v>4</v>
       </c>
       <c r="C419">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="D419">
         <f t="shared" si="6"/>
-        <v>-68104</v>
+        <v>23092</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A420" s="1">
-        <v>45379</v>
+        <v>45384</v>
       </c>
       <c r="B420" t="s">
         <v>4</v>
       </c>
       <c r="C420">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D420">
         <f t="shared" si="6"/>
-        <v>-68304</v>
+        <v>22962</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" s="1">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="B421" t="s">
         <v>4</v>
       </c>
       <c r="C421">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D421">
         <f t="shared" si="6"/>
-        <v>-68704</v>
+        <v>22532</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A422" s="1">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="B422" t="s">
         <v>4</v>
       </c>
       <c r="C422">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D422">
         <f t="shared" si="6"/>
-        <v>-68804</v>
+        <v>22412</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" s="1">
-        <v>45377</v>
+        <v>45384</v>
       </c>
       <c r="B423" t="s">
         <v>4</v>
       </c>
       <c r="C423">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D423">
         <f t="shared" si="6"/>
-        <v>-68854</v>
+        <v>22316</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" s="1">
-        <v>45377</v>
+        <v>45384</v>
       </c>
       <c r="B424" t="s">
         <v>4</v>
       </c>
       <c r="C424">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D424">
         <f t="shared" si="6"/>
-        <v>-68934</v>
+        <v>22206</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" s="1">
-        <v>45377</v>
+        <v>45383</v>
       </c>
       <c r="B425" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C425">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="D425">
         <f t="shared" si="6"/>
-        <v>-69034</v>
+        <v>32206</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A426" s="1">
-        <v>45377</v>
+        <v>45380</v>
       </c>
       <c r="B426" t="s">
         <v>4</v>
       </c>
       <c r="C426">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D426">
         <f t="shared" si="6"/>
-        <v>-69076</v>
+        <v>32156</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A427" s="1">
-        <v>45376</v>
+        <v>45380</v>
       </c>
       <c r="B427" t="s">
         <v>4</v>
       </c>
       <c r="C427">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="D427">
         <f t="shared" si="6"/>
-        <v>-69091</v>
+        <v>32046</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A428" s="1">
-        <v>45376</v>
+        <v>45379</v>
       </c>
       <c r="B428" t="s">
         <v>4</v>
       </c>
       <c r="C428">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D428">
         <f t="shared" si="6"/>
-        <v>-69161</v>
+        <v>31946</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A429" s="1">
-        <v>45376</v>
+        <v>45379</v>
       </c>
       <c r="B429" t="s">
         <v>4</v>
       </c>
       <c r="C429">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="D429">
         <f t="shared" si="6"/>
-        <v>-69381</v>
+        <v>31896</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" s="1">
-        <v>45375</v>
+        <v>45379</v>
       </c>
       <c r="B430" t="s">
         <v>4</v>
       </c>
       <c r="C430">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D430">
         <f t="shared" si="6"/>
-        <v>-69481</v>
+        <v>31696</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A431" s="1">
-        <v>45375</v>
+        <v>45378</v>
       </c>
       <c r="B431" t="s">
         <v>4</v>
       </c>
       <c r="C431">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D431">
         <f t="shared" si="6"/>
-        <v>-69601</v>
+        <v>31296</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A432" s="1">
-        <v>45373</v>
+        <v>45378</v>
       </c>
       <c r="B432" t="s">
         <v>4</v>
       </c>
       <c r="C432">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D432">
         <f t="shared" si="6"/>
-        <v>-69691</v>
+        <v>31196</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" s="1">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="B433" t="s">
         <v>4</v>
       </c>
       <c r="C433">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D433">
         <f t="shared" si="6"/>
-        <v>-69791</v>
+        <v>31146</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A434" s="1">
-        <v>45372</v>
+        <v>45377</v>
       </c>
       <c r="B434" t="s">
         <v>4</v>
       </c>
       <c r="C434">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D434">
         <f t="shared" si="6"/>
-        <v>-69851</v>
+        <v>31066</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A435" s="1">
-        <v>45372</v>
+        <v>45377</v>
       </c>
       <c r="B435" t="s">
         <v>4</v>
       </c>
       <c r="C435">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D435">
         <f t="shared" si="6"/>
-        <v>-69911</v>
+        <v>30966</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A436" s="1">
-        <v>45372</v>
+        <v>45377</v>
       </c>
       <c r="B436" t="s">
         <v>4</v>
       </c>
       <c r="C436">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D436">
         <f t="shared" si="6"/>
-        <v>-70031</v>
+        <v>30924</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A437" s="1">
-        <v>45372</v>
+        <v>45376</v>
       </c>
       <c r="B437" t="s">
         <v>4</v>
       </c>
       <c r="C437">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D437">
         <f t="shared" si="6"/>
-        <v>-70131</v>
+        <v>30909</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A438" s="1">
-        <v>45372</v>
+        <v>45376</v>
       </c>
       <c r="B438" t="s">
         <v>4</v>
       </c>
       <c r="C438">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D438">
         <f t="shared" si="6"/>
-        <v>-70181</v>
+        <v>30839</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" s="1">
-        <v>45372</v>
+        <v>45376</v>
       </c>
       <c r="B439" t="s">
         <v>4</v>
       </c>
       <c r="C439">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D439">
         <f t="shared" si="6"/>
-        <v>-70391</v>
+        <v>30619</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A440" s="1">
-        <v>45372</v>
+        <v>45375</v>
       </c>
       <c r="B440" t="s">
         <v>4</v>
       </c>
       <c r="C440">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="D440">
         <f t="shared" si="6"/>
-        <v>-71891</v>
+        <v>30519</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" s="1">
-        <v>45372</v>
+        <v>45375</v>
       </c>
       <c r="B441" t="s">
         <v>4</v>
       </c>
       <c r="C441">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="D441">
         <f t="shared" si="6"/>
-        <v>-72479</v>
+        <v>30399</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" s="1">
-        <v>45371</v>
+        <v>45373</v>
       </c>
       <c r="B442" t="s">
         <v>4</v>
       </c>
       <c r="C442">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D442">
         <f t="shared" si="6"/>
-        <v>-72609</v>
+        <v>30309</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A443" s="1">
-        <v>45371</v>
+        <v>45373</v>
       </c>
       <c r="B443" t="s">
         <v>4</v>
       </c>
       <c r="C443">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D443">
         <f t="shared" si="6"/>
-        <v>-72679</v>
+        <v>30209</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A444" s="1">
-        <v>45370</v>
+        <v>45372</v>
       </c>
       <c r="B444" t="s">
         <v>4</v>
       </c>
       <c r="C444">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D444">
         <f t="shared" si="6"/>
-        <v>-72706</v>
+        <v>30149</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A445" s="1">
-        <v>45370</v>
+        <v>45372</v>
       </c>
       <c r="B445" t="s">
         <v>4</v>
       </c>
       <c r="C445">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D445">
         <f t="shared" si="6"/>
-        <v>-72796</v>
+        <v>30089</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A446" s="1">
-        <v>45370</v>
+        <v>45372</v>
       </c>
       <c r="B446" t="s">
         <v>4</v>
       </c>
       <c r="C446">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D446">
         <f t="shared" si="6"/>
-        <v>-72906</v>
+        <v>29969</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A447" s="1">
-        <v>45370</v>
+        <v>45372</v>
       </c>
       <c r="B447" t="s">
         <v>4</v>
       </c>
       <c r="C447">
-        <v>435</v>
+        <v>100</v>
       </c>
       <c r="D447">
         <f t="shared" si="6"/>
-        <v>-73341</v>
+        <v>29869</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" s="1">
-        <v>45369</v>
+        <v>45372</v>
       </c>
       <c r="B448" t="s">
         <v>4</v>
       </c>
       <c r="C448">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D448">
         <f t="shared" si="6"/>
-        <v>-73441</v>
+        <v>29819</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" s="1">
-        <v>45369</v>
+        <v>45372</v>
       </c>
       <c r="B449" t="s">
         <v>4</v>
       </c>
       <c r="C449">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="D449">
         <f t="shared" si="6"/>
-        <v>-73551</v>
+        <v>29609</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" s="1">
-        <v>45367</v>
+        <v>45372</v>
       </c>
       <c r="B450" t="s">
         <v>4</v>
       </c>
       <c r="C450">
-        <v>50</v>
+        <v>1500</v>
       </c>
       <c r="D450">
         <f t="shared" si="6"/>
-        <v>-73601</v>
+        <v>28109</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" s="1">
-        <v>45367</v>
+        <v>45372</v>
       </c>
       <c r="B451" t="s">
         <v>4</v>
       </c>
       <c r="C451">
-        <v>30</v>
+        <v>588</v>
       </c>
       <c r="D451">
         <f t="shared" si="6"/>
-        <v>-73631</v>
+        <v>27521</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" s="1">
-        <v>45366</v>
+        <v>45371</v>
       </c>
       <c r="B452" t="s">
         <v>4</v>
       </c>
       <c r="C452">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="D452">
         <f t="shared" ref="D452:D515" si="7">IF(B452="Income",D451+C452,D451-C452)</f>
-        <v>-73686</v>
+        <v>27391</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" s="1">
-        <v>45366</v>
+        <v>45371</v>
       </c>
       <c r="B453" t="s">
         <v>4</v>
       </c>
       <c r="C453">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D453">
         <f t="shared" si="7"/>
-        <v>-73796</v>
+        <v>27321</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" s="1">
-        <v>45365</v>
+        <v>45370</v>
       </c>
       <c r="B454" t="s">
         <v>4</v>
       </c>
       <c r="C454">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D454">
         <f t="shared" si="7"/>
-        <v>-73870</v>
+        <v>27294</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" s="1">
-        <v>45365</v>
+        <v>45370</v>
       </c>
       <c r="B455" t="s">
         <v>4</v>
       </c>
       <c r="C455">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D455">
         <f t="shared" si="7"/>
-        <v>-73920</v>
+        <v>27204</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" s="1">
-        <v>45365</v>
+        <v>45370</v>
       </c>
       <c r="B456" t="s">
         <v>4</v>
       </c>
       <c r="C456">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D456">
         <f t="shared" si="7"/>
-        <v>-74040</v>
+        <v>27094</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" s="1">
-        <v>45365</v>
+        <v>45370</v>
       </c>
       <c r="B457" t="s">
         <v>4</v>
       </c>
       <c r="C457">
-        <v>50</v>
+        <v>435</v>
       </c>
       <c r="D457">
         <f t="shared" si="7"/>
-        <v>-74090</v>
+        <v>26659</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A458" s="1">
-        <v>45365</v>
+        <v>45369</v>
       </c>
       <c r="B458" t="s">
         <v>4</v>
       </c>
       <c r="C458">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D458">
         <f t="shared" si="7"/>
-        <v>-74140</v>
+        <v>26559</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A459" s="1">
-        <v>45365</v>
+        <v>45369</v>
       </c>
       <c r="B459" t="s">
         <v>4</v>
       </c>
       <c r="C459">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D459">
         <f t="shared" si="7"/>
-        <v>-74230</v>
+        <v>26449</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" s="1">
-        <v>45365</v>
+        <v>45367</v>
       </c>
       <c r="B460" t="s">
         <v>4</v>
       </c>
       <c r="C460">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="D460">
         <f t="shared" si="7"/>
-        <v>-74420</v>
+        <v>26399</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A461" s="1">
-        <v>45364</v>
+        <v>45367</v>
       </c>
       <c r="B461" t="s">
         <v>4</v>
       </c>
       <c r="C461">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="D461">
         <f t="shared" si="7"/>
-        <v>-74560</v>
+        <v>26369</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A462" s="1">
-        <v>45364</v>
+        <v>45366</v>
       </c>
       <c r="B462" t="s">
         <v>4</v>
       </c>
       <c r="C462">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="D462">
         <f t="shared" si="7"/>
-        <v>-74840</v>
+        <v>26314</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" s="1">
-        <v>45363</v>
+        <v>45366</v>
       </c>
       <c r="B463" t="s">
         <v>4</v>
       </c>
       <c r="C463">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="D463">
         <f t="shared" si="7"/>
-        <v>-74865</v>
+        <v>26204</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A464" s="1">
-        <v>45363</v>
+        <v>45365</v>
       </c>
       <c r="B464" t="s">
         <v>4</v>
       </c>
       <c r="C464">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D464">
         <f t="shared" si="7"/>
-        <v>-74950</v>
+        <v>26130</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" s="1">
-        <v>45363</v>
+        <v>45365</v>
       </c>
       <c r="B465" t="s">
         <v>4</v>
       </c>
       <c r="C465">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D465">
         <f t="shared" si="7"/>
-        <v>-74995</v>
+        <v>26080</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A466" s="1">
-        <v>45363</v>
+        <v>45365</v>
       </c>
       <c r="B466" t="s">
         <v>4</v>
       </c>
       <c r="C466">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D466">
         <f t="shared" si="7"/>
-        <v>-75075</v>
+        <v>25960</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A467" s="1">
-        <v>45362</v>
+        <v>45365</v>
       </c>
       <c r="B467" t="s">
         <v>4</v>
       </c>
       <c r="C467">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D467">
         <f t="shared" si="7"/>
-        <v>-75225</v>
+        <v>25910</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A468" s="1">
-        <v>45362</v>
+        <v>45365</v>
       </c>
       <c r="B468" t="s">
         <v>4</v>
       </c>
       <c r="C468">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D468">
         <f t="shared" si="7"/>
-        <v>-75285</v>
+        <v>25860</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" s="1">
-        <v>45362</v>
+        <v>45365</v>
       </c>
       <c r="B469" t="s">
         <v>4</v>
       </c>
       <c r="C469">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D469">
         <f t="shared" si="7"/>
-        <v>-75385</v>
+        <v>25770</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A470" s="1">
-        <v>45359</v>
+        <v>45365</v>
       </c>
       <c r="B470" t="s">
         <v>4</v>
       </c>
       <c r="C470">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="D470">
         <f t="shared" si="7"/>
-        <v>-75465</v>
+        <v>25580</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A471" s="1">
-        <v>45358</v>
+        <v>45364</v>
       </c>
       <c r="B471" t="s">
         <v>4</v>
       </c>
       <c r="C471">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="D471">
         <f t="shared" si="7"/>
-        <v>-75636</v>
+        <v>25440</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A472" s="1">
-        <v>45358</v>
+        <v>45364</v>
       </c>
       <c r="B472" t="s">
         <v>4</v>
       </c>
       <c r="C472">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="D472">
         <f t="shared" si="7"/>
-        <v>-75971</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" s="1">
-        <v>45357</v>
+        <v>45363</v>
       </c>
       <c r="B473" t="s">
         <v>4</v>
       </c>
       <c r="C473">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D473">
         <f t="shared" si="7"/>
-        <v>-76031</v>
+        <v>25135</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A474" s="1">
-        <v>45357</v>
+        <v>45363</v>
       </c>
       <c r="B474" t="s">
         <v>4</v>
       </c>
       <c r="C474">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D474">
         <f t="shared" si="7"/>
-        <v>-76096</v>
+        <v>25050</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A475" s="1">
-        <v>45357</v>
+        <v>45363</v>
       </c>
       <c r="B475" t="s">
         <v>4</v>
       </c>
       <c r="C475">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="D475">
         <f t="shared" si="7"/>
-        <v>-76197</v>
+        <v>25005</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A476" s="1">
-        <v>45356</v>
+        <v>45363</v>
       </c>
       <c r="B476" t="s">
         <v>4</v>
       </c>
       <c r="C476">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D476">
         <f t="shared" si="7"/>
-        <v>-76227</v>
+        <v>24925</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A477" s="1">
-        <v>45356</v>
+        <v>45362</v>
       </c>
       <c r="B477" t="s">
         <v>4</v>
       </c>
       <c r="C477">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="D477">
         <f t="shared" si="7"/>
-        <v>-76487</v>
+        <v>24775</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" s="1">
-        <v>45356</v>
+        <v>45362</v>
       </c>
       <c r="B478" t="s">
         <v>4</v>
@@ -7613,627 +7617,627 @@
       </c>
       <c r="D478">
         <f t="shared" si="7"/>
-        <v>-76547</v>
+        <v>24715</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A479" s="1">
-        <v>45355</v>
+        <v>45362</v>
       </c>
       <c r="B479" t="s">
         <v>4</v>
       </c>
       <c r="C479">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D479">
         <f t="shared" si="7"/>
-        <v>-76602</v>
+        <v>24615</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A480" s="1">
-        <v>45355</v>
+        <v>45359</v>
       </c>
       <c r="B480" t="s">
         <v>4</v>
       </c>
       <c r="C480">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D480">
         <f t="shared" si="7"/>
-        <v>-76702</v>
+        <v>24535</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" s="1">
-        <v>45352</v>
+        <v>45358</v>
       </c>
       <c r="B481" t="s">
         <v>4</v>
       </c>
       <c r="C481">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="D481">
         <f t="shared" si="7"/>
-        <v>-76803</v>
+        <v>24364</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A482" s="1">
-        <v>45352</v>
+        <v>45358</v>
       </c>
       <c r="B482" t="s">
         <v>4</v>
       </c>
       <c r="C482">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="D482">
         <f t="shared" si="7"/>
-        <v>-76983</v>
+        <v>24029</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A483" s="1">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B483" t="s">
         <v>4</v>
       </c>
       <c r="C483">
-        <v>564</v>
+        <v>60</v>
       </c>
       <c r="D483">
         <f t="shared" si="7"/>
-        <v>-77547</v>
+        <v>23969</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A484" s="1">
-        <v>45350</v>
+        <v>45357</v>
       </c>
       <c r="B484" t="s">
         <v>4</v>
       </c>
       <c r="C484">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D484">
         <f t="shared" si="7"/>
-        <v>-77597</v>
+        <v>23904</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A485" s="1">
-        <v>45350</v>
+        <v>45357</v>
       </c>
       <c r="B485" t="s">
         <v>4</v>
       </c>
       <c r="C485">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="D485">
         <f t="shared" si="7"/>
-        <v>-78004</v>
+        <v>23803</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A486" s="1">
-        <v>45350</v>
+        <v>45356</v>
       </c>
       <c r="B486" t="s">
         <v>4</v>
       </c>
       <c r="C486">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="D486">
         <f t="shared" si="7"/>
-        <v>-78088</v>
+        <v>23773</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" s="1">
-        <v>45350</v>
+        <v>45356</v>
       </c>
       <c r="B487" t="s">
         <v>4</v>
       </c>
       <c r="C487">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="D487">
         <f t="shared" si="7"/>
-        <v>-78128</v>
+        <v>23513</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A488" s="1">
-        <v>45350</v>
+        <v>45356</v>
       </c>
       <c r="B488" t="s">
         <v>4</v>
       </c>
       <c r="C488">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D488">
         <f t="shared" si="7"/>
-        <v>-78278</v>
+        <v>23453</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" s="1">
-        <v>45349</v>
+        <v>45355</v>
       </c>
       <c r="B489" t="s">
         <v>4</v>
       </c>
       <c r="C489">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D489">
         <f t="shared" si="7"/>
-        <v>-78330</v>
+        <v>23398</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" s="1">
-        <v>45349</v>
+        <v>45355</v>
       </c>
       <c r="B490" t="s">
         <v>4</v>
       </c>
       <c r="C490">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D490">
         <f t="shared" si="7"/>
-        <v>-78930</v>
+        <v>23298</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A491" s="1">
-        <v>45349</v>
+        <v>45352</v>
       </c>
       <c r="B491" t="s">
         <v>4</v>
       </c>
       <c r="C491">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="D491">
         <f t="shared" si="7"/>
-        <v>-79065</v>
+        <v>23197</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A492" s="1">
-        <v>45345</v>
+        <v>45352</v>
       </c>
       <c r="B492" t="s">
         <v>4</v>
       </c>
       <c r="C492">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="D492">
         <f t="shared" si="7"/>
-        <v>-79210</v>
+        <v>23017</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A493" s="1">
-        <v>45345</v>
+        <v>45352</v>
       </c>
       <c r="B493" t="s">
         <v>4</v>
       </c>
       <c r="C493">
-        <v>18</v>
+        <v>564</v>
       </c>
       <c r="D493">
         <f t="shared" si="7"/>
-        <v>-79228</v>
+        <v>22453</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A494" s="1">
-        <v>45345</v>
+        <v>45352</v>
       </c>
       <c r="B494" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C494">
-        <v>134</v>
+        <v>10000</v>
       </c>
       <c r="D494">
         <f t="shared" si="7"/>
-        <v>-79362</v>
+        <v>32453</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A495" s="1">
-        <v>45345</v>
+        <v>45350</v>
       </c>
       <c r="B495" t="s">
         <v>4</v>
       </c>
       <c r="C495">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="D495">
         <f t="shared" si="7"/>
-        <v>-79662</v>
+        <v>32403</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" s="1">
-        <v>45345</v>
+        <v>45350</v>
       </c>
       <c r="B496" t="s">
         <v>4</v>
       </c>
       <c r="C496">
-        <v>100</v>
+        <v>407</v>
       </c>
       <c r="D496">
         <f t="shared" si="7"/>
-        <v>-79762</v>
+        <v>31996</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" s="1">
-        <v>45344</v>
+        <v>45350</v>
       </c>
       <c r="B497" t="s">
         <v>4</v>
       </c>
       <c r="C497">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D497">
         <f t="shared" si="7"/>
-        <v>-79812</v>
+        <v>31912</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" s="1">
-        <v>45344</v>
+        <v>45350</v>
       </c>
       <c r="B498" t="s">
         <v>4</v>
       </c>
       <c r="C498">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D498">
         <f t="shared" si="7"/>
-        <v>-79867</v>
+        <v>31872</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" s="1">
-        <v>45344</v>
+        <v>45350</v>
       </c>
       <c r="B499" t="s">
         <v>4</v>
       </c>
       <c r="C499">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="D499">
         <f t="shared" si="7"/>
-        <v>-80051</v>
+        <v>31722</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" s="1">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="B500" t="s">
         <v>4</v>
       </c>
       <c r="C500">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="D500">
         <f t="shared" si="7"/>
-        <v>-80186</v>
+        <v>31670</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" s="1">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="B501" t="s">
         <v>4</v>
       </c>
       <c r="C501">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="D501">
         <f t="shared" si="7"/>
-        <v>-80296</v>
+        <v>31070</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" s="1">
-        <v>45342</v>
+        <v>45349</v>
       </c>
       <c r="B502" t="s">
         <v>4</v>
       </c>
       <c r="C502">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="D502">
         <f t="shared" si="7"/>
-        <v>-80351</v>
+        <v>30935</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" s="1">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="B503" t="s">
         <v>4</v>
       </c>
       <c r="C503">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="D503">
         <f t="shared" si="7"/>
-        <v>-80461</v>
+        <v>30790</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" s="1">
-        <v>45341</v>
+        <v>45345</v>
       </c>
       <c r="B504" t="s">
         <v>4</v>
       </c>
       <c r="C504">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="D504">
         <f t="shared" si="7"/>
-        <v>-80646</v>
+        <v>30772</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" s="1">
-        <v>45341</v>
+        <v>45345</v>
       </c>
       <c r="B505" t="s">
         <v>4</v>
       </c>
       <c r="C505">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="D505">
         <f t="shared" si="7"/>
-        <v>-80685</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A506" s="1">
-        <v>45341</v>
+        <v>45345</v>
       </c>
       <c r="B506" t="s">
         <v>4</v>
       </c>
       <c r="C506">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D506">
         <f t="shared" si="7"/>
-        <v>-80785</v>
+        <v>30338</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A507" s="1">
-        <v>45339</v>
+        <v>45345</v>
       </c>
       <c r="B507" t="s">
         <v>4</v>
       </c>
       <c r="C507">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D507">
         <f t="shared" si="7"/>
-        <v>-80870</v>
+        <v>30238</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" s="1">
-        <v>45339</v>
+        <v>45344</v>
       </c>
       <c r="B508" t="s">
         <v>4</v>
       </c>
       <c r="C508">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D508">
         <f t="shared" si="7"/>
-        <v>-80931</v>
+        <v>30188</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" s="1">
-        <v>45339</v>
+        <v>45344</v>
       </c>
       <c r="B509" t="s">
         <v>4</v>
       </c>
       <c r="C509">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D509">
         <f t="shared" si="7"/>
-        <v>-81031</v>
+        <v>30133</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" s="1">
-        <v>45338</v>
+        <v>45344</v>
       </c>
       <c r="B510" t="s">
         <v>4</v>
       </c>
       <c r="C510">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="D510">
         <f t="shared" si="7"/>
-        <v>-81132</v>
+        <v>29949</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" s="1">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="B511" t="s">
         <v>4</v>
       </c>
       <c r="C511">
-        <v>265</v>
+        <v>135</v>
       </c>
       <c r="D511">
         <f t="shared" si="7"/>
-        <v>-81397</v>
+        <v>29814</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" s="1">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="B512" t="s">
         <v>4</v>
       </c>
       <c r="C512">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D512">
         <f t="shared" si="7"/>
-        <v>-81452</v>
+        <v>29704</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" s="1">
-        <v>45337</v>
+        <v>45342</v>
       </c>
       <c r="B513" t="s">
         <v>4</v>
       </c>
       <c r="C513">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D513">
         <f t="shared" si="7"/>
-        <v>-81552</v>
+        <v>29649</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" s="1">
-        <v>45336</v>
+        <v>45342</v>
       </c>
       <c r="B514" t="s">
         <v>4</v>
       </c>
       <c r="C514">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D514">
         <f t="shared" si="7"/>
-        <v>-81657</v>
+        <v>29539</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" s="1">
-        <v>45336</v>
+        <v>45341</v>
       </c>
       <c r="B515" t="s">
         <v>4</v>
       </c>
       <c r="C515">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="D515">
         <f t="shared" si="7"/>
-        <v>-81722</v>
+        <v>29354</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" s="1">
-        <v>45329</v>
+        <v>45341</v>
       </c>
       <c r="B516" t="s">
         <v>4</v>
       </c>
       <c r="C516">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="D516">
-        <f t="shared" ref="D516:D553" si="8">IF(B516="Income",D515+C516,D515-C516)</f>
-        <v>-81922</v>
+        <f t="shared" ref="D516:D566" si="8">IF(B516="Income",D515+C516,D515-C516)</f>
+        <v>29315</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" s="1">
-        <v>45329</v>
+        <v>45341</v>
       </c>
       <c r="B517" t="s">
         <v>4</v>
       </c>
       <c r="C517">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D517">
         <f t="shared" si="8"/>
-        <v>-82422</v>
+        <v>29215</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" s="1">
-        <v>45320</v>
+        <v>45339</v>
       </c>
       <c r="B518" t="s">
         <v>4</v>
       </c>
       <c r="C518">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="D518">
         <f t="shared" si="8"/>
-        <v>-82772</v>
+        <v>29130</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" s="1">
-        <v>45320</v>
+        <v>45339</v>
       </c>
       <c r="B519" t="s">
         <v>4</v>
       </c>
       <c r="C519">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="D519">
         <f t="shared" si="8"/>
-        <v>-83002</v>
+        <v>29069</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" s="1">
-        <v>45320</v>
+        <v>45339</v>
       </c>
       <c r="B520" t="s">
         <v>4</v>
@@ -8243,177 +8247,177 @@
       </c>
       <c r="D520">
         <f t="shared" si="8"/>
-        <v>-83102</v>
+        <v>28969</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" s="1">
-        <v>45315</v>
+        <v>45338</v>
       </c>
       <c r="B521" t="s">
         <v>4</v>
       </c>
       <c r="C521">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="D521">
         <f t="shared" si="8"/>
-        <v>-83288</v>
+        <v>28868</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" s="1">
-        <v>45315</v>
+        <v>45337</v>
       </c>
       <c r="B522" t="s">
         <v>4</v>
       </c>
       <c r="C522">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="D522">
         <f t="shared" si="8"/>
-        <v>-83388</v>
+        <v>28603</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" s="1">
-        <v>45315</v>
+        <v>45337</v>
       </c>
       <c r="B523" t="s">
         <v>4</v>
       </c>
       <c r="C523">
-        <v>400</v>
+        <v>55</v>
       </c>
       <c r="D523">
         <f t="shared" si="8"/>
-        <v>-83788</v>
+        <v>28548</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" s="1">
-        <v>45313</v>
+        <v>45337</v>
       </c>
       <c r="B524" t="s">
         <v>4</v>
       </c>
       <c r="C524">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D524">
         <f t="shared" si="8"/>
-        <v>-83818</v>
+        <v>28448</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" s="1">
-        <v>45313</v>
+        <v>45336</v>
       </c>
       <c r="B525" t="s">
         <v>4</v>
       </c>
       <c r="C525">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="D525">
         <f t="shared" si="8"/>
-        <v>-83878</v>
+        <v>28343</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" s="1">
-        <v>45313</v>
+        <v>45336</v>
       </c>
       <c r="B526" t="s">
         <v>4</v>
       </c>
       <c r="C526">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D526">
         <f t="shared" si="8"/>
-        <v>-83928</v>
+        <v>28278</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" s="1">
-        <v>45313</v>
+        <v>45329</v>
       </c>
       <c r="B527" t="s">
         <v>4</v>
       </c>
       <c r="C527">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="D527">
         <f t="shared" si="8"/>
-        <v>-84153</v>
+        <v>28078</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" s="1">
-        <v>45313</v>
+        <v>45329</v>
       </c>
       <c r="B528" t="s">
         <v>4</v>
       </c>
       <c r="C528">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D528">
         <f t="shared" si="8"/>
-        <v>-84253</v>
+        <v>27578</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" s="1">
-        <v>45312</v>
+        <v>45323</v>
       </c>
       <c r="B529" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C529">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="D529">
         <f t="shared" si="8"/>
-        <v>-84283</v>
+        <v>37578</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" s="1">
-        <v>45312</v>
+        <v>45320</v>
       </c>
       <c r="B530" t="s">
         <v>4</v>
       </c>
       <c r="C530">
-        <v>465</v>
+        <v>350</v>
       </c>
       <c r="D530">
         <f t="shared" si="8"/>
-        <v>-84748</v>
+        <v>37228</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" s="1">
-        <v>45309</v>
+        <v>45320</v>
       </c>
       <c r="B531" t="s">
         <v>4</v>
       </c>
       <c r="C531">
-        <v>3500</v>
+        <v>230</v>
       </c>
       <c r="D531">
         <f t="shared" si="8"/>
-        <v>-88248</v>
+        <v>36998</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" s="1">
-        <v>45309</v>
+        <v>45320</v>
       </c>
       <c r="B532" t="s">
         <v>4</v>
@@ -8423,322 +8427,517 @@
       </c>
       <c r="D532">
         <f t="shared" si="8"/>
-        <v>-88348</v>
+        <v>36898</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" s="1">
-        <v>45309</v>
+        <v>45315</v>
       </c>
       <c r="B533" t="s">
         <v>4</v>
       </c>
       <c r="C533">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="D533">
         <f t="shared" si="8"/>
-        <v>-88603</v>
+        <v>36712</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" s="1">
-        <v>45307</v>
+        <v>45315</v>
       </c>
       <c r="B534" t="s">
         <v>4</v>
       </c>
       <c r="C534">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D534">
         <f t="shared" si="8"/>
-        <v>-88803</v>
+        <v>36612</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" s="1">
-        <v>45307</v>
+        <v>45315</v>
       </c>
       <c r="B535" t="s">
         <v>4</v>
       </c>
       <c r="C535">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="D535">
         <f t="shared" si="8"/>
-        <v>-88853</v>
+        <v>36212</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" s="1">
-        <v>45307</v>
+        <v>45313</v>
       </c>
       <c r="B536" t="s">
         <v>4</v>
       </c>
       <c r="C536">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D536">
         <f t="shared" si="8"/>
-        <v>-88943</v>
+        <v>36182</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" s="1">
-        <v>45307</v>
+        <v>45313</v>
       </c>
       <c r="B537" t="s">
         <v>4</v>
       </c>
       <c r="C537">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D537">
         <f t="shared" si="8"/>
-        <v>-89143</v>
+        <v>36122</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" s="1">
-        <v>45306</v>
+        <v>45313</v>
       </c>
       <c r="B538" t="s">
         <v>4</v>
       </c>
       <c r="C538">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D538">
         <f t="shared" si="8"/>
-        <v>-89247</v>
+        <v>36072</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" s="1">
-        <v>45306</v>
+        <v>45313</v>
       </c>
       <c r="B539" t="s">
         <v>4</v>
       </c>
       <c r="C539">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="D539">
         <f t="shared" si="8"/>
-        <v>-89347</v>
+        <v>35847</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" s="1">
-        <v>45302</v>
+        <v>45313</v>
       </c>
       <c r="B540" t="s">
         <v>4</v>
       </c>
       <c r="C540">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D540">
         <f t="shared" si="8"/>
-        <v>-89443</v>
+        <v>35747</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" s="1">
-        <v>45302</v>
+        <v>45312</v>
       </c>
       <c r="B541" t="s">
         <v>4</v>
       </c>
       <c r="C541">
-        <v>305</v>
+        <v>30</v>
       </c>
       <c r="D541">
         <f t="shared" si="8"/>
-        <v>-89748</v>
+        <v>35717</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" s="1">
-        <v>45302</v>
+        <v>45312</v>
       </c>
       <c r="B542" t="s">
         <v>4</v>
       </c>
       <c r="C542">
-        <v>100</v>
+        <v>465</v>
       </c>
       <c r="D542">
         <f t="shared" si="8"/>
-        <v>-89848</v>
+        <v>35252</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" s="1">
-        <v>45302</v>
+        <v>45309</v>
       </c>
       <c r="B543" t="s">
         <v>4</v>
       </c>
       <c r="C543">
-        <v>292</v>
+        <v>3500</v>
       </c>
       <c r="D543">
         <f t="shared" si="8"/>
-        <v>-90140</v>
+        <v>31752</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" s="1">
-        <v>45302</v>
+        <v>45309</v>
       </c>
       <c r="B544" t="s">
         <v>4</v>
       </c>
       <c r="C544">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D544">
         <f t="shared" si="8"/>
-        <v>-90290</v>
+        <v>31652</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" s="1">
-        <v>45301</v>
+        <v>45309</v>
       </c>
       <c r="B545" t="s">
         <v>4</v>
       </c>
       <c r="C545">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="D545">
         <f t="shared" si="8"/>
-        <v>-90430</v>
+        <v>31397</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A546" s="1">
-        <v>45301</v>
+        <v>45307</v>
       </c>
       <c r="B546" t="s">
         <v>4</v>
       </c>
       <c r="C546">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D546">
         <f t="shared" si="8"/>
-        <v>-90530</v>
+        <v>31197</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A547" s="1">
-        <v>45301</v>
+        <v>45307</v>
       </c>
       <c r="B547" t="s">
         <v>4</v>
       </c>
       <c r="C547">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D547">
         <f t="shared" si="8"/>
-        <v>-90590</v>
+        <v>31147</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A548" s="1">
-        <v>45301</v>
+        <v>45307</v>
       </c>
       <c r="B548" t="s">
         <v>4</v>
       </c>
       <c r="C548">
-        <v>410</v>
+        <v>90</v>
       </c>
       <c r="D548">
         <f t="shared" si="8"/>
-        <v>-91000</v>
+        <v>31057</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A549" s="1">
-        <v>45301</v>
+        <v>45307</v>
       </c>
       <c r="B549" t="s">
         <v>4</v>
       </c>
       <c r="C549">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="D549">
         <f t="shared" si="8"/>
-        <v>-91110</v>
+        <v>30857</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" s="1">
-        <v>45300</v>
+        <v>45306</v>
       </c>
       <c r="B550" t="s">
         <v>4</v>
       </c>
       <c r="C550">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D550">
         <f t="shared" si="8"/>
-        <v>-91240</v>
+        <v>30753</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A551" s="1">
-        <v>45300</v>
+        <v>45306</v>
       </c>
       <c r="B551" t="s">
         <v>4</v>
       </c>
       <c r="C551">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D551">
         <f t="shared" si="8"/>
-        <v>-91365</v>
+        <v>30653</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A552" s="1">
-        <v>45299</v>
+        <v>45302</v>
       </c>
       <c r="B552" t="s">
         <v>4</v>
       </c>
       <c r="C552">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D552">
         <f t="shared" si="8"/>
-        <v>-91453</v>
+        <v>30557</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" s="1">
-        <v>45299</v>
+        <v>45302</v>
       </c>
       <c r="B553" t="s">
         <v>4</v>
       </c>
       <c r="C553">
-        <v>110</v>
+        <v>305</v>
       </c>
       <c r="D553">
         <f t="shared" si="8"/>
-        <v>-91563</v>
+        <v>30252</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A554" s="1">
+        <v>45302</v>
+      </c>
+      <c r="B554" t="s">
+        <v>4</v>
+      </c>
+      <c r="C554">
+        <v>100</v>
+      </c>
+      <c r="D554">
+        <f t="shared" si="8"/>
+        <v>30152</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A555" s="1">
+        <v>45302</v>
+      </c>
+      <c r="B555" t="s">
+        <v>4</v>
+      </c>
+      <c r="C555">
+        <v>292</v>
+      </c>
+      <c r="D555">
+        <f t="shared" si="8"/>
+        <v>29860</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A556" s="1">
+        <v>45302</v>
+      </c>
+      <c r="B556" t="s">
+        <v>4</v>
+      </c>
+      <c r="C556">
+        <v>150</v>
+      </c>
+      <c r="D556">
+        <f t="shared" si="8"/>
+        <v>29710</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A557" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B557" t="s">
+        <v>4</v>
+      </c>
+      <c r="C557">
+        <v>140</v>
+      </c>
+      <c r="D557">
+        <f t="shared" si="8"/>
+        <v>29570</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A558" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B558" t="s">
+        <v>4</v>
+      </c>
+      <c r="C558">
+        <v>100</v>
+      </c>
+      <c r="D558">
+        <f t="shared" si="8"/>
+        <v>29470</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A559" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B559" t="s">
+        <v>4</v>
+      </c>
+      <c r="C559">
+        <v>60</v>
+      </c>
+      <c r="D559">
+        <f t="shared" si="8"/>
+        <v>29410</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A560" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B560" t="s">
+        <v>4</v>
+      </c>
+      <c r="C560">
+        <v>410</v>
+      </c>
+      <c r="D560">
+        <f t="shared" si="8"/>
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A561" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B561" t="s">
+        <v>4</v>
+      </c>
+      <c r="C561">
+        <v>110</v>
+      </c>
+      <c r="D561">
+        <f t="shared" si="8"/>
+        <v>28890</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A562" s="1">
+        <v>45300</v>
+      </c>
+      <c r="B562" t="s">
+        <v>4</v>
+      </c>
+      <c r="C562">
+        <v>130</v>
+      </c>
+      <c r="D562">
+        <f t="shared" si="8"/>
+        <v>28760</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A563" s="1">
+        <v>45300</v>
+      </c>
+      <c r="B563" t="s">
+        <v>4</v>
+      </c>
+      <c r="C563">
+        <v>125</v>
+      </c>
+      <c r="D563">
+        <f t="shared" si="8"/>
+        <v>28635</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A564" s="1">
+        <v>45299</v>
+      </c>
+      <c r="B564" t="s">
+        <v>4</v>
+      </c>
+      <c r="C564">
+        <v>88</v>
+      </c>
+      <c r="D564">
+        <f t="shared" si="8"/>
+        <v>28547</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A565" s="1">
+        <v>45299</v>
+      </c>
+      <c r="B565" t="s">
+        <v>4</v>
+      </c>
+      <c r="C565">
+        <v>110</v>
+      </c>
+      <c r="D565">
+        <f t="shared" si="8"/>
+        <v>28437</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A566" s="1">
+        <v>45292</v>
+      </c>
+      <c r="B566" t="s">
+        <v>5</v>
+      </c>
+      <c r="C566">
+        <v>10000</v>
+      </c>
+      <c r="D566">
+        <f t="shared" si="8"/>
+        <v>38437</v>
       </c>
     </row>
   </sheetData>
